--- a/train_log.xlsx
+++ b/train_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G721"/>
+  <dimension ref="A1:G745"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1308,7 +1308,7 @@
         <v>7.39</v>
       </c>
       <c r="E33" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
         <v>9.58</v>
@@ -6357,7 +6357,7 @@
         <v>0</v>
       </c>
       <c r="E220" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F220" t="n">
         <v>0</v>
@@ -12735,7 +12735,7 @@
         <v>0</v>
       </c>
       <c r="G456" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="457">
@@ -12762,7 +12762,7 @@
         <v>0</v>
       </c>
       <c r="G457" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="458">
@@ -19891,6 +19891,654 @@
       </c>
       <c r="G721" t="n">
         <v>1.8</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C722" t="n">
+        <v>0</v>
+      </c>
+      <c r="D722" t="n">
+        <v>0</v>
+      </c>
+      <c r="E722" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F722" t="n">
+        <v>0</v>
+      </c>
+      <c r="G722" t="n">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C723" t="n">
+        <v>0</v>
+      </c>
+      <c r="D723" t="n">
+        <v>0</v>
+      </c>
+      <c r="E723" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="F723" t="n">
+        <v>0</v>
+      </c>
+      <c r="G723" t="n">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C724" t="n">
+        <v>0</v>
+      </c>
+      <c r="D724" t="n">
+        <v>0</v>
+      </c>
+      <c r="E724" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F724" t="n">
+        <v>0</v>
+      </c>
+      <c r="G724" t="n">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C725" t="n">
+        <v>0</v>
+      </c>
+      <c r="D725" t="n">
+        <v>0</v>
+      </c>
+      <c r="E725" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="F725" t="n">
+        <v>0</v>
+      </c>
+      <c r="G725" t="n">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C726" t="n">
+        <v>0</v>
+      </c>
+      <c r="D726" t="n">
+        <v>0</v>
+      </c>
+      <c r="E726" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="F726" t="n">
+        <v>0</v>
+      </c>
+      <c r="G726" t="n">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C727" t="n">
+        <v>0</v>
+      </c>
+      <c r="D727" t="n">
+        <v>0</v>
+      </c>
+      <c r="E727" t="n">
+        <v>10</v>
+      </c>
+      <c r="F727" t="n">
+        <v>0</v>
+      </c>
+      <c r="G727" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C728" t="n">
+        <v>0</v>
+      </c>
+      <c r="D728" t="n">
+        <v>0</v>
+      </c>
+      <c r="E728" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="F728" t="n">
+        <v>0</v>
+      </c>
+      <c r="G728" t="n">
+        <v>9.699999999999999</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C729" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="D729" t="n">
+        <v>6</v>
+      </c>
+      <c r="E729" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F729" t="n">
+        <v>6</v>
+      </c>
+      <c r="G729" t="n">
+        <v>9.800000000000001</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C730" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="D730" t="n">
+        <v>71</v>
+      </c>
+      <c r="E730" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F730" t="n">
+        <v>71</v>
+      </c>
+      <c r="G730" t="n">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C731" t="n">
+        <v>13.38</v>
+      </c>
+      <c r="D731" t="n">
+        <v>164</v>
+      </c>
+      <c r="E731" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F731" t="n">
+        <v>164</v>
+      </c>
+      <c r="G731" t="n">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C732" t="n">
+        <v>34.04</v>
+      </c>
+      <c r="D732" t="n">
+        <v>419</v>
+      </c>
+      <c r="E732" t="n">
+        <v>13</v>
+      </c>
+      <c r="F732" t="n">
+        <v>419</v>
+      </c>
+      <c r="G732" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C733" t="n">
+        <v>19.83</v>
+      </c>
+      <c r="D733" t="n">
+        <v>243</v>
+      </c>
+      <c r="E733" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F733" t="n">
+        <v>243</v>
+      </c>
+      <c r="G733" t="n">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C734" t="n">
+        <v>14.36</v>
+      </c>
+      <c r="D734" t="n">
+        <v>176</v>
+      </c>
+      <c r="E734" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="F734" t="n">
+        <v>176</v>
+      </c>
+      <c r="G734" t="n">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C735" t="n">
+        <v>19.42</v>
+      </c>
+      <c r="D735" t="n">
+        <v>238</v>
+      </c>
+      <c r="E735" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F735" t="n">
+        <v>238</v>
+      </c>
+      <c r="G735" t="n">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C736" t="n">
+        <v>24.89</v>
+      </c>
+      <c r="D736" t="n">
+        <v>305</v>
+      </c>
+      <c r="E736" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F736" t="n">
+        <v>305</v>
+      </c>
+      <c r="G736" t="n">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C737" t="n">
+        <v>18.93</v>
+      </c>
+      <c r="D737" t="n">
+        <v>232</v>
+      </c>
+      <c r="E737" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F737" t="n">
+        <v>232</v>
+      </c>
+      <c r="G737" t="n">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C738" t="n">
+        <v>17.71</v>
+      </c>
+      <c r="D738" t="n">
+        <v>217</v>
+      </c>
+      <c r="E738" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="F738" t="n">
+        <v>217</v>
+      </c>
+      <c r="G738" t="n">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C739" t="n">
+        <v>10.93</v>
+      </c>
+      <c r="D739" t="n">
+        <v>134</v>
+      </c>
+      <c r="E739" t="n">
+        <v>12</v>
+      </c>
+      <c r="F739" t="n">
+        <v>134</v>
+      </c>
+      <c r="G739" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C740" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="D740" t="n">
+        <v>88</v>
+      </c>
+      <c r="E740" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="F740" t="n">
+        <v>88</v>
+      </c>
+      <c r="G740" t="n">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C741" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="D741" t="n">
+        <v>17</v>
+      </c>
+      <c r="E741" t="n">
+        <v>10</v>
+      </c>
+      <c r="F741" t="n">
+        <v>17</v>
+      </c>
+      <c r="G741" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C742" t="n">
+        <v>0</v>
+      </c>
+      <c r="D742" t="n">
+        <v>0</v>
+      </c>
+      <c r="E742" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F742" t="n">
+        <v>0</v>
+      </c>
+      <c r="G742" t="n">
+        <v>9.800000000000001</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C743" t="n">
+        <v>0</v>
+      </c>
+      <c r="D743" t="n">
+        <v>0</v>
+      </c>
+      <c r="E743" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="F743" t="n">
+        <v>0</v>
+      </c>
+      <c r="G743" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C744" t="n">
+        <v>0</v>
+      </c>
+      <c r="D744" t="n">
+        <v>0</v>
+      </c>
+      <c r="E744" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="F744" t="n">
+        <v>0</v>
+      </c>
+      <c r="G744" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C745" t="n">
+        <v>0</v>
+      </c>
+      <c r="D745" t="n">
+        <v>0</v>
+      </c>
+      <c r="E745" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="F745" t="n">
+        <v>0</v>
+      </c>
+      <c r="G745" t="n">
+        <v>8.9</v>
       </c>
     </row>
   </sheetData>

--- a/train_log.xlsx
+++ b/train_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G745"/>
+  <dimension ref="A1:G841"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20541,6 +20541,2598 @@
         <v>8.9</v>
       </c>
     </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C746" t="n">
+        <v>0</v>
+      </c>
+      <c r="D746" t="n">
+        <v>0</v>
+      </c>
+      <c r="E746" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="F746" t="n">
+        <v>0</v>
+      </c>
+      <c r="G746" t="n">
+        <v>8.800000000000001</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C747" t="n">
+        <v>0</v>
+      </c>
+      <c r="D747" t="n">
+        <v>0</v>
+      </c>
+      <c r="E747" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="F747" t="n">
+        <v>0</v>
+      </c>
+      <c r="G747" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C748" t="n">
+        <v>0</v>
+      </c>
+      <c r="D748" t="n">
+        <v>0</v>
+      </c>
+      <c r="E748" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="F748" t="n">
+        <v>0</v>
+      </c>
+      <c r="G748" t="n">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C749" t="n">
+        <v>0</v>
+      </c>
+      <c r="D749" t="n">
+        <v>0</v>
+      </c>
+      <c r="E749" t="n">
+        <v>7</v>
+      </c>
+      <c r="F749" t="n">
+        <v>0</v>
+      </c>
+      <c r="G749" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C750" t="n">
+        <v>0</v>
+      </c>
+      <c r="D750" t="n">
+        <v>0</v>
+      </c>
+      <c r="E750" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F750" t="n">
+        <v>0</v>
+      </c>
+      <c r="G750" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C751" t="n">
+        <v>0</v>
+      </c>
+      <c r="D751" t="n">
+        <v>0</v>
+      </c>
+      <c r="E751" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F751" t="n">
+        <v>0</v>
+      </c>
+      <c r="G751" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C752" t="n">
+        <v>0</v>
+      </c>
+      <c r="D752" t="n">
+        <v>0</v>
+      </c>
+      <c r="E752" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="F752" t="n">
+        <v>0</v>
+      </c>
+      <c r="G752" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C753" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="D753" t="n">
+        <v>25</v>
+      </c>
+      <c r="E753" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F753" t="n">
+        <v>25</v>
+      </c>
+      <c r="G753" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C754" t="n">
+        <v>14.36</v>
+      </c>
+      <c r="D754" t="n">
+        <v>176</v>
+      </c>
+      <c r="E754" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="F754" t="n">
+        <v>176</v>
+      </c>
+      <c r="G754" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C755" t="n">
+        <v>31.17</v>
+      </c>
+      <c r="D755" t="n">
+        <v>382</v>
+      </c>
+      <c r="E755" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="F755" t="n">
+        <v>382</v>
+      </c>
+      <c r="G755" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C756" t="n">
+        <v>46.04</v>
+      </c>
+      <c r="D756" t="n">
+        <v>577</v>
+      </c>
+      <c r="E756" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F756" t="n">
+        <v>577</v>
+      </c>
+      <c r="G756" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C757" t="n">
+        <v>56.89</v>
+      </c>
+      <c r="D757" t="n">
+        <v>734</v>
+      </c>
+      <c r="E757" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="F757" t="n">
+        <v>734</v>
+      </c>
+      <c r="G757" t="n">
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C758" t="n">
+        <v>63.73</v>
+      </c>
+      <c r="D758" t="n">
+        <v>838</v>
+      </c>
+      <c r="E758" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="F758" t="n">
+        <v>838</v>
+      </c>
+      <c r="G758" t="n">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C759" t="n">
+        <v>65.65000000000001</v>
+      </c>
+      <c r="D759" t="n">
+        <v>872</v>
+      </c>
+      <c r="E759" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="F759" t="n">
+        <v>872</v>
+      </c>
+      <c r="G759" t="n">
+        <v>17.1</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C760" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="D760" t="n">
+        <v>839</v>
+      </c>
+      <c r="E760" t="n">
+        <v>18</v>
+      </c>
+      <c r="F760" t="n">
+        <v>839</v>
+      </c>
+      <c r="G760" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C761" t="n">
+        <v>56.49</v>
+      </c>
+      <c r="D761" t="n">
+        <v>740</v>
+      </c>
+      <c r="E761" t="n">
+        <v>18</v>
+      </c>
+      <c r="F761" t="n">
+        <v>740</v>
+      </c>
+      <c r="G761" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C762" t="n">
+        <v>45.74</v>
+      </c>
+      <c r="D762" t="n">
+        <v>588</v>
+      </c>
+      <c r="E762" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="F762" t="n">
+        <v>588</v>
+      </c>
+      <c r="G762" t="n">
+        <v>18.3</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C763" t="n">
+        <v>31.75</v>
+      </c>
+      <c r="D763" t="n">
+        <v>397</v>
+      </c>
+      <c r="E763" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F763" t="n">
+        <v>397</v>
+      </c>
+      <c r="G763" t="n">
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C764" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="D764" t="n">
+        <v>190</v>
+      </c>
+      <c r="E764" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="F764" t="n">
+        <v>190</v>
+      </c>
+      <c r="G764" t="n">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C765" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="D765" t="n">
+        <v>31</v>
+      </c>
+      <c r="E765" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F765" t="n">
+        <v>31</v>
+      </c>
+      <c r="G765" t="n">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C766" t="n">
+        <v>0</v>
+      </c>
+      <c r="D766" t="n">
+        <v>0</v>
+      </c>
+      <c r="E766" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F766" t="n">
+        <v>0</v>
+      </c>
+      <c r="G766" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C767" t="n">
+        <v>0</v>
+      </c>
+      <c r="D767" t="n">
+        <v>0</v>
+      </c>
+      <c r="E767" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F767" t="n">
+        <v>0</v>
+      </c>
+      <c r="G767" t="n">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C768" t="n">
+        <v>0</v>
+      </c>
+      <c r="D768" t="n">
+        <v>0</v>
+      </c>
+      <c r="E768" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F768" t="n">
+        <v>0</v>
+      </c>
+      <c r="G768" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C769" t="n">
+        <v>0</v>
+      </c>
+      <c r="D769" t="n">
+        <v>0</v>
+      </c>
+      <c r="E769" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="F769" t="n">
+        <v>0</v>
+      </c>
+      <c r="G769" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C770" t="n">
+        <v>0</v>
+      </c>
+      <c r="D770" t="n">
+        <v>0</v>
+      </c>
+      <c r="E770" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="F770" t="n">
+        <v>0</v>
+      </c>
+      <c r="G770" t="n">
+        <v>8.800000000000001</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C771" t="n">
+        <v>0</v>
+      </c>
+      <c r="D771" t="n">
+        <v>0</v>
+      </c>
+      <c r="E771" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="F771" t="n">
+        <v>0</v>
+      </c>
+      <c r="G771" t="n">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C772" t="n">
+        <v>0</v>
+      </c>
+      <c r="D772" t="n">
+        <v>0</v>
+      </c>
+      <c r="E772" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="F772" t="n">
+        <v>0</v>
+      </c>
+      <c r="G772" t="n">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C773" t="n">
+        <v>0</v>
+      </c>
+      <c r="D773" t="n">
+        <v>0</v>
+      </c>
+      <c r="E773" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="F773" t="n">
+        <v>0</v>
+      </c>
+      <c r="G773" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C774" t="n">
+        <v>0</v>
+      </c>
+      <c r="D774" t="n">
+        <v>0</v>
+      </c>
+      <c r="E774" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="F774" t="n">
+        <v>0</v>
+      </c>
+      <c r="G774" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C775" t="n">
+        <v>0</v>
+      </c>
+      <c r="D775" t="n">
+        <v>0</v>
+      </c>
+      <c r="E775" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="F775" t="n">
+        <v>0</v>
+      </c>
+      <c r="G775" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C776" t="n">
+        <v>0</v>
+      </c>
+      <c r="D776" t="n">
+        <v>0</v>
+      </c>
+      <c r="E776" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F776" t="n">
+        <v>0</v>
+      </c>
+      <c r="G776" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C777" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="D777" t="n">
+        <v>24</v>
+      </c>
+      <c r="E777" t="n">
+        <v>6</v>
+      </c>
+      <c r="F777" t="n">
+        <v>24</v>
+      </c>
+      <c r="G777" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C778" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="D778" t="n">
+        <v>127</v>
+      </c>
+      <c r="E778" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F778" t="n">
+        <v>127</v>
+      </c>
+      <c r="G778" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C779" t="n">
+        <v>26.36</v>
+      </c>
+      <c r="D779" t="n">
+        <v>323</v>
+      </c>
+      <c r="E779" t="n">
+        <v>9</v>
+      </c>
+      <c r="F779" t="n">
+        <v>323</v>
+      </c>
+      <c r="G779" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C780" t="n">
+        <v>47.01</v>
+      </c>
+      <c r="D780" t="n">
+        <v>586</v>
+      </c>
+      <c r="E780" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F780" t="n">
+        <v>586</v>
+      </c>
+      <c r="G780" t="n">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C781" t="n">
+        <v>58.73</v>
+      </c>
+      <c r="D781" t="n">
+        <v>753</v>
+      </c>
+      <c r="E781" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F781" t="n">
+        <v>753</v>
+      </c>
+      <c r="G781" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C782" t="n">
+        <v>54.56</v>
+      </c>
+      <c r="D782" t="n">
+        <v>696</v>
+      </c>
+      <c r="E782" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="F782" t="n">
+        <v>696</v>
+      </c>
+      <c r="G782" t="n">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C783" t="n">
+        <v>66.92</v>
+      </c>
+      <c r="D783" t="n">
+        <v>879</v>
+      </c>
+      <c r="E783" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="F783" t="n">
+        <v>879</v>
+      </c>
+      <c r="G783" t="n">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C784" t="n">
+        <v>59.44</v>
+      </c>
+      <c r="D784" t="n">
+        <v>771</v>
+      </c>
+      <c r="E784" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="F784" t="n">
+        <v>771</v>
+      </c>
+      <c r="G784" t="n">
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C785" t="n">
+        <v>54.43</v>
+      </c>
+      <c r="D785" t="n">
+        <v>701</v>
+      </c>
+      <c r="E785" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="F785" t="n">
+        <v>701</v>
+      </c>
+      <c r="G785" t="n">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C786" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="D786" t="n">
+        <v>588</v>
+      </c>
+      <c r="E786" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="F786" t="n">
+        <v>588</v>
+      </c>
+      <c r="G786" t="n">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C787" t="n">
+        <v>32.24</v>
+      </c>
+      <c r="D787" t="n">
+        <v>398</v>
+      </c>
+      <c r="E787" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="F787" t="n">
+        <v>398</v>
+      </c>
+      <c r="G787" t="n">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C788" t="n">
+        <v>15.91</v>
+      </c>
+      <c r="D788" t="n">
+        <v>195</v>
+      </c>
+      <c r="E788" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F788" t="n">
+        <v>195</v>
+      </c>
+      <c r="G788" t="n">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C789" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="D789" t="n">
+        <v>34</v>
+      </c>
+      <c r="E789" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F789" t="n">
+        <v>34</v>
+      </c>
+      <c r="G789" t="n">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C790" t="n">
+        <v>0</v>
+      </c>
+      <c r="D790" t="n">
+        <v>0</v>
+      </c>
+      <c r="E790" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="F790" t="n">
+        <v>0</v>
+      </c>
+      <c r="G790" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C791" t="n">
+        <v>0</v>
+      </c>
+      <c r="D791" t="n">
+        <v>0</v>
+      </c>
+      <c r="E791" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="F791" t="n">
+        <v>0</v>
+      </c>
+      <c r="G791" t="n">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C792" t="n">
+        <v>0</v>
+      </c>
+      <c r="D792" t="n">
+        <v>0</v>
+      </c>
+      <c r="E792" t="n">
+        <v>9</v>
+      </c>
+      <c r="F792" t="n">
+        <v>0</v>
+      </c>
+      <c r="G792" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C793" t="n">
+        <v>0</v>
+      </c>
+      <c r="D793" t="n">
+        <v>0</v>
+      </c>
+      <c r="E793" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="F793" t="n">
+        <v>0</v>
+      </c>
+      <c r="G793" t="n">
+        <v>8.800000000000001</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C794" t="n">
+        <v>0</v>
+      </c>
+      <c r="D794" t="n">
+        <v>0</v>
+      </c>
+      <c r="E794" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="F794" t="n">
+        <v>0</v>
+      </c>
+      <c r="G794" t="n">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C795" t="n">
+        <v>0</v>
+      </c>
+      <c r="D795" t="n">
+        <v>0</v>
+      </c>
+      <c r="E795" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="F795" t="n">
+        <v>0</v>
+      </c>
+      <c r="G795" t="n">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C796" t="n">
+        <v>0</v>
+      </c>
+      <c r="D796" t="n">
+        <v>0</v>
+      </c>
+      <c r="E796" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="F796" t="n">
+        <v>0</v>
+      </c>
+      <c r="G796" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C797" t="n">
+        <v>0</v>
+      </c>
+      <c r="D797" t="n">
+        <v>0</v>
+      </c>
+      <c r="E797" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="F797" t="n">
+        <v>0</v>
+      </c>
+      <c r="G797" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C798" t="n">
+        <v>0</v>
+      </c>
+      <c r="D798" t="n">
+        <v>0</v>
+      </c>
+      <c r="E798" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="F798" t="n">
+        <v>0</v>
+      </c>
+      <c r="G798" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C799" t="n">
+        <v>0</v>
+      </c>
+      <c r="D799" t="n">
+        <v>0</v>
+      </c>
+      <c r="E799" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F799" t="n">
+        <v>0</v>
+      </c>
+      <c r="G799" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C800" t="n">
+        <v>0</v>
+      </c>
+      <c r="D800" t="n">
+        <v>0</v>
+      </c>
+      <c r="E800" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F800" t="n">
+        <v>0</v>
+      </c>
+      <c r="G800" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C801" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D801" t="n">
+        <v>22</v>
+      </c>
+      <c r="E801" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="F801" t="n">
+        <v>22</v>
+      </c>
+      <c r="G801" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C802" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="D802" t="n">
+        <v>114</v>
+      </c>
+      <c r="E802" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="F802" t="n">
+        <v>114</v>
+      </c>
+      <c r="G802" t="n">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C803" t="n">
+        <v>28.23</v>
+      </c>
+      <c r="D803" t="n">
+        <v>346</v>
+      </c>
+      <c r="E803" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="F803" t="n">
+        <v>346</v>
+      </c>
+      <c r="G803" t="n">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C804" t="n">
+        <v>45.64</v>
+      </c>
+      <c r="D804" t="n">
+        <v>578</v>
+      </c>
+      <c r="E804" t="n">
+        <v>15</v>
+      </c>
+      <c r="F804" t="n">
+        <v>578</v>
+      </c>
+      <c r="G804" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C805" t="n">
+        <v>54.58</v>
+      </c>
+      <c r="D805" t="n">
+        <v>706</v>
+      </c>
+      <c r="E805" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="F805" t="n">
+        <v>706</v>
+      </c>
+      <c r="G805" t="n">
+        <v>16.1</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C806" t="n">
+        <v>59.49</v>
+      </c>
+      <c r="D806" t="n">
+        <v>779</v>
+      </c>
+      <c r="E806" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="F806" t="n">
+        <v>779</v>
+      </c>
+      <c r="G806" t="n">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C807" t="n">
+        <v>63.19</v>
+      </c>
+      <c r="D807" t="n">
+        <v>836</v>
+      </c>
+      <c r="E807" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="F807" t="n">
+        <v>836</v>
+      </c>
+      <c r="G807" t="n">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C808" t="n">
+        <v>60.91</v>
+      </c>
+      <c r="D808" t="n">
+        <v>803</v>
+      </c>
+      <c r="E808" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F808" t="n">
+        <v>803</v>
+      </c>
+      <c r="G808" t="n">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C809" t="n">
+        <v>38.15</v>
+      </c>
+      <c r="D809" t="n">
+        <v>480</v>
+      </c>
+      <c r="E809" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="F809" t="n">
+        <v>480</v>
+      </c>
+      <c r="G809" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C810" t="n">
+        <v>25.79</v>
+      </c>
+      <c r="D810" t="n">
+        <v>316</v>
+      </c>
+      <c r="E810" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="F810" t="n">
+        <v>316</v>
+      </c>
+      <c r="G810" t="n">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C811" t="n">
+        <v>13.14</v>
+      </c>
+      <c r="D811" t="n">
+        <v>161</v>
+      </c>
+      <c r="E811" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F811" t="n">
+        <v>161</v>
+      </c>
+      <c r="G811" t="n">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C812" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="D812" t="n">
+        <v>50</v>
+      </c>
+      <c r="E812" t="n">
+        <v>13</v>
+      </c>
+      <c r="F812" t="n">
+        <v>50</v>
+      </c>
+      <c r="G812" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C813" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="D813" t="n">
+        <v>8</v>
+      </c>
+      <c r="E813" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F813" t="n">
+        <v>8</v>
+      </c>
+      <c r="G813" t="n">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C814" t="n">
+        <v>0</v>
+      </c>
+      <c r="D814" t="n">
+        <v>0</v>
+      </c>
+      <c r="E814" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="F814" t="n">
+        <v>0</v>
+      </c>
+      <c r="G814" t="n">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C815" t="n">
+        <v>0</v>
+      </c>
+      <c r="D815" t="n">
+        <v>0</v>
+      </c>
+      <c r="E815" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F815" t="n">
+        <v>0</v>
+      </c>
+      <c r="G815" t="n">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C816" t="n">
+        <v>0</v>
+      </c>
+      <c r="D816" t="n">
+        <v>0</v>
+      </c>
+      <c r="E816" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="F816" t="n">
+        <v>0</v>
+      </c>
+      <c r="G816" t="n">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C817" t="n">
+        <v>0</v>
+      </c>
+      <c r="D817" t="n">
+        <v>0</v>
+      </c>
+      <c r="E817" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F817" t="n">
+        <v>0</v>
+      </c>
+      <c r="G817" t="n">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C818" t="n">
+        <v>0</v>
+      </c>
+      <c r="D818" t="n">
+        <v>0</v>
+      </c>
+      <c r="E818" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="F818" t="n">
+        <v>0</v>
+      </c>
+      <c r="G818" t="n">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C819" t="n">
+        <v>0</v>
+      </c>
+      <c r="D819" t="n">
+        <v>0</v>
+      </c>
+      <c r="E819" t="n">
+        <v>10</v>
+      </c>
+      <c r="F819" t="n">
+        <v>0</v>
+      </c>
+      <c r="G819" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C820" t="n">
+        <v>0</v>
+      </c>
+      <c r="D820" t="n">
+        <v>0</v>
+      </c>
+      <c r="E820" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F820" t="n">
+        <v>0</v>
+      </c>
+      <c r="G820" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C821" t="n">
+        <v>0</v>
+      </c>
+      <c r="D821" t="n">
+        <v>0</v>
+      </c>
+      <c r="E821" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="F821" t="n">
+        <v>0</v>
+      </c>
+      <c r="G821" t="n">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C822" t="n">
+        <v>0</v>
+      </c>
+      <c r="D822" t="n">
+        <v>0</v>
+      </c>
+      <c r="E822" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F822" t="n">
+        <v>0</v>
+      </c>
+      <c r="G822" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C823" t="n">
+        <v>0</v>
+      </c>
+      <c r="D823" t="n">
+        <v>0</v>
+      </c>
+      <c r="E823" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F823" t="n">
+        <v>0</v>
+      </c>
+      <c r="G823" t="n">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C824" t="n">
+        <v>0</v>
+      </c>
+      <c r="D824" t="n">
+        <v>0</v>
+      </c>
+      <c r="E824" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F824" t="n">
+        <v>0</v>
+      </c>
+      <c r="G824" t="n">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C825" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D825" t="n">
+        <v>4</v>
+      </c>
+      <c r="E825" t="n">
+        <v>12</v>
+      </c>
+      <c r="F825" t="n">
+        <v>4</v>
+      </c>
+      <c r="G825" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C826" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="D826" t="n">
+        <v>7</v>
+      </c>
+      <c r="E826" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F826" t="n">
+        <v>7</v>
+      </c>
+      <c r="G826" t="n">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C827" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="D827" t="n">
+        <v>16</v>
+      </c>
+      <c r="E827" t="n">
+        <v>11</v>
+      </c>
+      <c r="F827" t="n">
+        <v>16</v>
+      </c>
+      <c r="G827" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C828" t="n">
+        <v>12.89</v>
+      </c>
+      <c r="D828" t="n">
+        <v>158</v>
+      </c>
+      <c r="E828" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="F828" t="n">
+        <v>158</v>
+      </c>
+      <c r="G828" t="n">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C829" t="n">
+        <v>18.93</v>
+      </c>
+      <c r="D829" t="n">
+        <v>232</v>
+      </c>
+      <c r="E829" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F829" t="n">
+        <v>232</v>
+      </c>
+      <c r="G829" t="n">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C830" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="D830" t="n">
+        <v>212</v>
+      </c>
+      <c r="E830" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="F830" t="n">
+        <v>212</v>
+      </c>
+      <c r="G830" t="n">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C831" t="n">
+        <v>31.92</v>
+      </c>
+      <c r="D831" t="n">
+        <v>396</v>
+      </c>
+      <c r="E831" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="F831" t="n">
+        <v>396</v>
+      </c>
+      <c r="G831" t="n">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C832" t="n">
+        <v>53.95</v>
+      </c>
+      <c r="D832" t="n">
+        <v>705</v>
+      </c>
+      <c r="E832" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F832" t="n">
+        <v>705</v>
+      </c>
+      <c r="G832" t="n">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C833" t="n">
+        <v>36.05</v>
+      </c>
+      <c r="D833" t="n">
+        <v>453</v>
+      </c>
+      <c r="E833" t="n">
+        <v>17</v>
+      </c>
+      <c r="F833" t="n">
+        <v>453</v>
+      </c>
+      <c r="G833" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C834" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="D834" t="n">
+        <v>333</v>
+      </c>
+      <c r="E834" t="n">
+        <v>18</v>
+      </c>
+      <c r="F834" t="n">
+        <v>333</v>
+      </c>
+      <c r="G834" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C835" t="n">
+        <v>27.59</v>
+      </c>
+      <c r="D835" t="n">
+        <v>343</v>
+      </c>
+      <c r="E835" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F835" t="n">
+        <v>343</v>
+      </c>
+      <c r="G835" t="n">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C836" t="n">
+        <v>14.28</v>
+      </c>
+      <c r="D836" t="n">
+        <v>175</v>
+      </c>
+      <c r="E836" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="F836" t="n">
+        <v>175</v>
+      </c>
+      <c r="G836" t="n">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C837" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="D837" t="n">
+        <v>31</v>
+      </c>
+      <c r="E837" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F837" t="n">
+        <v>31</v>
+      </c>
+      <c r="G837" t="n">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C838" t="n">
+        <v>0</v>
+      </c>
+      <c r="D838" t="n">
+        <v>0</v>
+      </c>
+      <c r="E838" t="n">
+        <v>11</v>
+      </c>
+      <c r="F838" t="n">
+        <v>0</v>
+      </c>
+      <c r="G838" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C839" t="n">
+        <v>0</v>
+      </c>
+      <c r="D839" t="n">
+        <v>0</v>
+      </c>
+      <c r="E839" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F839" t="n">
+        <v>0</v>
+      </c>
+      <c r="G839" t="n">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C840" t="n">
+        <v>0</v>
+      </c>
+      <c r="D840" t="n">
+        <v>0</v>
+      </c>
+      <c r="E840" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F840" t="n">
+        <v>0</v>
+      </c>
+      <c r="G840" t="n">
+        <v>9.800000000000001</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C841" t="n">
+        <v>0</v>
+      </c>
+      <c r="D841" t="n">
+        <v>0</v>
+      </c>
+      <c r="E841" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="F841" t="n">
+        <v>0</v>
+      </c>
+      <c r="G841" t="n">
+        <v>9.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/train_log.xlsx
+++ b/train_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G841"/>
+  <dimension ref="A1:G1081"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23133,6 +23133,6486 @@
         <v>9.4</v>
       </c>
     </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C842" t="n">
+        <v>0</v>
+      </c>
+      <c r="D842" t="n">
+        <v>0</v>
+      </c>
+      <c r="E842" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="F842" t="n">
+        <v>0</v>
+      </c>
+      <c r="G842" t="n">
+        <v>8.800000000000001</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C843" t="n">
+        <v>0</v>
+      </c>
+      <c r="D843" t="n">
+        <v>0</v>
+      </c>
+      <c r="E843" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="F843" t="n">
+        <v>0</v>
+      </c>
+      <c r="G843" t="n">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C844" t="n">
+        <v>0</v>
+      </c>
+      <c r="D844" t="n">
+        <v>0</v>
+      </c>
+      <c r="E844" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="F844" t="n">
+        <v>0</v>
+      </c>
+      <c r="G844" t="n">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C845" t="n">
+        <v>0</v>
+      </c>
+      <c r="D845" t="n">
+        <v>0</v>
+      </c>
+      <c r="E845" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F845" t="n">
+        <v>0</v>
+      </c>
+      <c r="G845" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C846" t="n">
+        <v>0</v>
+      </c>
+      <c r="D846" t="n">
+        <v>0</v>
+      </c>
+      <c r="E846" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F846" t="n">
+        <v>0</v>
+      </c>
+      <c r="G846" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C847" t="n">
+        <v>0</v>
+      </c>
+      <c r="D847" t="n">
+        <v>0</v>
+      </c>
+      <c r="E847" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="F847" t="n">
+        <v>0</v>
+      </c>
+      <c r="G847" t="n">
+        <v>9.699999999999999</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C848" t="n">
+        <v>0</v>
+      </c>
+      <c r="D848" t="n">
+        <v>0</v>
+      </c>
+      <c r="E848" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="F848" t="n">
+        <v>0</v>
+      </c>
+      <c r="G848" t="n">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C849" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="D849" t="n">
+        <v>24</v>
+      </c>
+      <c r="E849" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="F849" t="n">
+        <v>24</v>
+      </c>
+      <c r="G849" t="n">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C850" t="n">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="D850" t="n">
+        <v>112</v>
+      </c>
+      <c r="E850" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="F850" t="n">
+        <v>112</v>
+      </c>
+      <c r="G850" t="n">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C851" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="D851" t="n">
+        <v>159</v>
+      </c>
+      <c r="E851" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="F851" t="n">
+        <v>159</v>
+      </c>
+      <c r="G851" t="n">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C852" t="n">
+        <v>22.03</v>
+      </c>
+      <c r="D852" t="n">
+        <v>270</v>
+      </c>
+      <c r="E852" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="F852" t="n">
+        <v>270</v>
+      </c>
+      <c r="G852" t="n">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C853" t="n">
+        <v>40.99</v>
+      </c>
+      <c r="D853" t="n">
+        <v>516</v>
+      </c>
+      <c r="E853" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="F853" t="n">
+        <v>516</v>
+      </c>
+      <c r="G853" t="n">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C854" t="n">
+        <v>47.53</v>
+      </c>
+      <c r="D854" t="n">
+        <v>608</v>
+      </c>
+      <c r="E854" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="F854" t="n">
+        <v>608</v>
+      </c>
+      <c r="G854" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C855" t="n">
+        <v>45.16</v>
+      </c>
+      <c r="D855" t="n">
+        <v>576</v>
+      </c>
+      <c r="E855" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="F855" t="n">
+        <v>576</v>
+      </c>
+      <c r="G855" t="n">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C856" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="D856" t="n">
+        <v>619</v>
+      </c>
+      <c r="E856" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F856" t="n">
+        <v>619</v>
+      </c>
+      <c r="G856" t="n">
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C857" t="n">
+        <v>30.33</v>
+      </c>
+      <c r="D857" t="n">
+        <v>378</v>
+      </c>
+      <c r="E857" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="F857" t="n">
+        <v>378</v>
+      </c>
+      <c r="G857" t="n">
+        <v>17.4</v>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C858" t="n">
+        <v>16.48</v>
+      </c>
+      <c r="D858" t="n">
+        <v>202</v>
+      </c>
+      <c r="E858" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="F858" t="n">
+        <v>202</v>
+      </c>
+      <c r="G858" t="n">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C859" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="D859" t="n">
+        <v>106</v>
+      </c>
+      <c r="E859" t="n">
+        <v>14</v>
+      </c>
+      <c r="F859" t="n">
+        <v>106</v>
+      </c>
+      <c r="G859" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C860" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="D860" t="n">
+        <v>48</v>
+      </c>
+      <c r="E860" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F860" t="n">
+        <v>48</v>
+      </c>
+      <c r="G860" t="n">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C861" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="D861" t="n">
+        <v>10</v>
+      </c>
+      <c r="E861" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="F861" t="n">
+        <v>10</v>
+      </c>
+      <c r="G861" t="n">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C862" t="n">
+        <v>0</v>
+      </c>
+      <c r="D862" t="n">
+        <v>0</v>
+      </c>
+      <c r="E862" t="n">
+        <v>12</v>
+      </c>
+      <c r="F862" t="n">
+        <v>0</v>
+      </c>
+      <c r="G862" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C863" t="n">
+        <v>0</v>
+      </c>
+      <c r="D863" t="n">
+        <v>0</v>
+      </c>
+      <c r="E863" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F863" t="n">
+        <v>0</v>
+      </c>
+      <c r="G863" t="n">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C864" t="n">
+        <v>0</v>
+      </c>
+      <c r="D864" t="n">
+        <v>0</v>
+      </c>
+      <c r="E864" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F864" t="n">
+        <v>0</v>
+      </c>
+      <c r="G864" t="n">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C865" t="n">
+        <v>0</v>
+      </c>
+      <c r="D865" t="n">
+        <v>0</v>
+      </c>
+      <c r="E865" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F865" t="n">
+        <v>0</v>
+      </c>
+      <c r="G865" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C866" t="n">
+        <v>0</v>
+      </c>
+      <c r="D866" t="n">
+        <v>0</v>
+      </c>
+      <c r="E866" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="F866" t="n">
+        <v>0</v>
+      </c>
+      <c r="G866" t="n">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C867" t="n">
+        <v>0</v>
+      </c>
+      <c r="D867" t="n">
+        <v>0</v>
+      </c>
+      <c r="E867" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="F867" t="n">
+        <v>0</v>
+      </c>
+      <c r="G867" t="n">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C868" t="n">
+        <v>0</v>
+      </c>
+      <c r="D868" t="n">
+        <v>0</v>
+      </c>
+      <c r="E868" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="F868" t="n">
+        <v>0</v>
+      </c>
+      <c r="G868" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C869" t="n">
+        <v>0</v>
+      </c>
+      <c r="D869" t="n">
+        <v>0</v>
+      </c>
+      <c r="E869" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="F869" t="n">
+        <v>0</v>
+      </c>
+      <c r="G869" t="n">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C870" t="n">
+        <v>0</v>
+      </c>
+      <c r="D870" t="n">
+        <v>0</v>
+      </c>
+      <c r="E870" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="F870" t="n">
+        <v>0</v>
+      </c>
+      <c r="G870" t="n">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C871" t="n">
+        <v>0</v>
+      </c>
+      <c r="D871" t="n">
+        <v>0</v>
+      </c>
+      <c r="E871" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="F871" t="n">
+        <v>0</v>
+      </c>
+      <c r="G871" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C872" t="n">
+        <v>0</v>
+      </c>
+      <c r="D872" t="n">
+        <v>0</v>
+      </c>
+      <c r="E872" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="F872" t="n">
+        <v>0</v>
+      </c>
+      <c r="G872" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C873" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="D873" t="n">
+        <v>35</v>
+      </c>
+      <c r="E873" t="n">
+        <v>5</v>
+      </c>
+      <c r="F873" t="n">
+        <v>35</v>
+      </c>
+      <c r="G873" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C874" t="n">
+        <v>16.56</v>
+      </c>
+      <c r="D874" t="n">
+        <v>203</v>
+      </c>
+      <c r="E874" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="F874" t="n">
+        <v>203</v>
+      </c>
+      <c r="G874" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C875" t="n">
+        <v>34.03</v>
+      </c>
+      <c r="D875" t="n">
+        <v>417</v>
+      </c>
+      <c r="E875" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="F875" t="n">
+        <v>417</v>
+      </c>
+      <c r="G875" t="n">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C876" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="D876" t="n">
+        <v>615</v>
+      </c>
+      <c r="E876" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="F876" t="n">
+        <v>615</v>
+      </c>
+      <c r="G876" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C877" t="n">
+        <v>60.77</v>
+      </c>
+      <c r="D877" t="n">
+        <v>773</v>
+      </c>
+      <c r="E877" t="n">
+        <v>10</v>
+      </c>
+      <c r="F877" t="n">
+        <v>773</v>
+      </c>
+      <c r="G877" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C878" t="n">
+        <v>67.61</v>
+      </c>
+      <c r="D878" t="n">
+        <v>874</v>
+      </c>
+      <c r="E878" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F878" t="n">
+        <v>874</v>
+      </c>
+      <c r="G878" t="n">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C879" t="n">
+        <v>69.79000000000001</v>
+      </c>
+      <c r="D879" t="n">
+        <v>910</v>
+      </c>
+      <c r="E879" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="F879" t="n">
+        <v>910</v>
+      </c>
+      <c r="G879" t="n">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C880" t="n">
+        <v>67.25</v>
+      </c>
+      <c r="D880" t="n">
+        <v>875</v>
+      </c>
+      <c r="E880" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F880" t="n">
+        <v>875</v>
+      </c>
+      <c r="G880" t="n">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C881" t="n">
+        <v>60.03</v>
+      </c>
+      <c r="D881" t="n">
+        <v>773</v>
+      </c>
+      <c r="E881" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="F881" t="n">
+        <v>773</v>
+      </c>
+      <c r="G881" t="n">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C882" t="n">
+        <v>48.58</v>
+      </c>
+      <c r="D882" t="n">
+        <v>614</v>
+      </c>
+      <c r="E882" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="F882" t="n">
+        <v>614</v>
+      </c>
+      <c r="G882" t="n">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C883" t="n">
+        <v>33.81</v>
+      </c>
+      <c r="D883" t="n">
+        <v>415</v>
+      </c>
+      <c r="E883" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F883" t="n">
+        <v>415</v>
+      </c>
+      <c r="G883" t="n">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C884" t="n">
+        <v>16.48</v>
+      </c>
+      <c r="D884" t="n">
+        <v>202</v>
+      </c>
+      <c r="E884" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F884" t="n">
+        <v>202</v>
+      </c>
+      <c r="G884" t="n">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C885" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="D885" t="n">
+        <v>37</v>
+      </c>
+      <c r="E885" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="F885" t="n">
+        <v>37</v>
+      </c>
+      <c r="G885" t="n">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C886" t="n">
+        <v>0</v>
+      </c>
+      <c r="D886" t="n">
+        <v>0</v>
+      </c>
+      <c r="E886" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F886" t="n">
+        <v>0</v>
+      </c>
+      <c r="G886" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C887" t="n">
+        <v>0</v>
+      </c>
+      <c r="D887" t="n">
+        <v>0</v>
+      </c>
+      <c r="E887" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="F887" t="n">
+        <v>0</v>
+      </c>
+      <c r="G887" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C888" t="n">
+        <v>0</v>
+      </c>
+      <c r="D888" t="n">
+        <v>0</v>
+      </c>
+      <c r="E888" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F888" t="n">
+        <v>0</v>
+      </c>
+      <c r="G888" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C889" t="n">
+        <v>0</v>
+      </c>
+      <c r="D889" t="n">
+        <v>0</v>
+      </c>
+      <c r="E889" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F889" t="n">
+        <v>0</v>
+      </c>
+      <c r="G889" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C890" t="n">
+        <v>0</v>
+      </c>
+      <c r="D890" t="n">
+        <v>0</v>
+      </c>
+      <c r="E890" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="F890" t="n">
+        <v>0</v>
+      </c>
+      <c r="G890" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C891" t="n">
+        <v>0</v>
+      </c>
+      <c r="D891" t="n">
+        <v>0</v>
+      </c>
+      <c r="E891" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="F891" t="n">
+        <v>0</v>
+      </c>
+      <c r="G891" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C892" t="n">
+        <v>0</v>
+      </c>
+      <c r="D892" t="n">
+        <v>0</v>
+      </c>
+      <c r="E892" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F892" t="n">
+        <v>0</v>
+      </c>
+      <c r="G892" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C893" t="n">
+        <v>0</v>
+      </c>
+      <c r="D893" t="n">
+        <v>0</v>
+      </c>
+      <c r="E893" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F893" t="n">
+        <v>0</v>
+      </c>
+      <c r="G893" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C894" t="n">
+        <v>0</v>
+      </c>
+      <c r="D894" t="n">
+        <v>0</v>
+      </c>
+      <c r="E894" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F894" t="n">
+        <v>0</v>
+      </c>
+      <c r="G894" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C895" t="n">
+        <v>0</v>
+      </c>
+      <c r="D895" t="n">
+        <v>0</v>
+      </c>
+      <c r="E895" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F895" t="n">
+        <v>0</v>
+      </c>
+      <c r="G895" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C896" t="n">
+        <v>0</v>
+      </c>
+      <c r="D896" t="n">
+        <v>0</v>
+      </c>
+      <c r="E896" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F896" t="n">
+        <v>0</v>
+      </c>
+      <c r="G896" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C897" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D897" t="n">
+        <v>38</v>
+      </c>
+      <c r="E897" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F897" t="n">
+        <v>38</v>
+      </c>
+      <c r="G897" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C898" t="n">
+        <v>16.81</v>
+      </c>
+      <c r="D898" t="n">
+        <v>206</v>
+      </c>
+      <c r="E898" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="F898" t="n">
+        <v>206</v>
+      </c>
+      <c r="G898" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C899" t="n">
+        <v>33.95</v>
+      </c>
+      <c r="D899" t="n">
+        <v>416</v>
+      </c>
+      <c r="E899" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F899" t="n">
+        <v>416</v>
+      </c>
+      <c r="G899" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C900" t="n">
+        <v>49.13</v>
+      </c>
+      <c r="D900" t="n">
+        <v>613</v>
+      </c>
+      <c r="E900" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F900" t="n">
+        <v>613</v>
+      </c>
+      <c r="G900" t="n">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C901" t="n">
+        <v>59.96</v>
+      </c>
+      <c r="D901" t="n">
+        <v>768</v>
+      </c>
+      <c r="E901" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="F901" t="n">
+        <v>768</v>
+      </c>
+      <c r="G901" t="n">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C902" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="D902" t="n">
+        <v>869</v>
+      </c>
+      <c r="E902" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="F902" t="n">
+        <v>869</v>
+      </c>
+      <c r="G902" t="n">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C903" t="n">
+        <v>68.63</v>
+      </c>
+      <c r="D903" t="n">
+        <v>902</v>
+      </c>
+      <c r="E903" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="F903" t="n">
+        <v>902</v>
+      </c>
+      <c r="G903" t="n">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C904" t="n">
+        <v>65.86</v>
+      </c>
+      <c r="D904" t="n">
+        <v>862</v>
+      </c>
+      <c r="E904" t="n">
+        <v>14</v>
+      </c>
+      <c r="F904" t="n">
+        <v>862</v>
+      </c>
+      <c r="G904" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C905" t="n">
+        <v>58.71</v>
+      </c>
+      <c r="D905" t="n">
+        <v>759</v>
+      </c>
+      <c r="E905" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="F905" t="n">
+        <v>759</v>
+      </c>
+      <c r="G905" t="n">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C906" t="n">
+        <v>47.79</v>
+      </c>
+      <c r="D906" t="n">
+        <v>604</v>
+      </c>
+      <c r="E906" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="F906" t="n">
+        <v>604</v>
+      </c>
+      <c r="G906" t="n">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C907" t="n">
+        <v>33.62</v>
+      </c>
+      <c r="D907" t="n">
+        <v>413</v>
+      </c>
+      <c r="E907" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F907" t="n">
+        <v>413</v>
+      </c>
+      <c r="G907" t="n">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C908" t="n">
+        <v>16.81</v>
+      </c>
+      <c r="D908" t="n">
+        <v>206</v>
+      </c>
+      <c r="E908" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F908" t="n">
+        <v>206</v>
+      </c>
+      <c r="G908" t="n">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C909" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D909" t="n">
+        <v>38</v>
+      </c>
+      <c r="E909" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="F909" t="n">
+        <v>38</v>
+      </c>
+      <c r="G909" t="n">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C910" t="n">
+        <v>0</v>
+      </c>
+      <c r="D910" t="n">
+        <v>0</v>
+      </c>
+      <c r="E910" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="F910" t="n">
+        <v>0</v>
+      </c>
+      <c r="G910" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C911" t="n">
+        <v>0</v>
+      </c>
+      <c r="D911" t="n">
+        <v>0</v>
+      </c>
+      <c r="E911" t="n">
+        <v>6</v>
+      </c>
+      <c r="F911" t="n">
+        <v>0</v>
+      </c>
+      <c r="G911" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C912" t="n">
+        <v>0</v>
+      </c>
+      <c r="D912" t="n">
+        <v>0</v>
+      </c>
+      <c r="E912" t="n">
+        <v>6</v>
+      </c>
+      <c r="F912" t="n">
+        <v>0</v>
+      </c>
+      <c r="G912" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C913" t="n">
+        <v>0</v>
+      </c>
+      <c r="D913" t="n">
+        <v>0</v>
+      </c>
+      <c r="E913" t="n">
+        <v>6</v>
+      </c>
+      <c r="F913" t="n">
+        <v>0</v>
+      </c>
+      <c r="G913" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C914" t="n">
+        <v>0</v>
+      </c>
+      <c r="D914" t="n">
+        <v>0</v>
+      </c>
+      <c r="E914" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="F914" t="n">
+        <v>0</v>
+      </c>
+      <c r="G914" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C915" t="n">
+        <v>0</v>
+      </c>
+      <c r="D915" t="n">
+        <v>0</v>
+      </c>
+      <c r="E915" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="F915" t="n">
+        <v>0</v>
+      </c>
+      <c r="G915" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C916" t="n">
+        <v>0</v>
+      </c>
+      <c r="D916" t="n">
+        <v>0</v>
+      </c>
+      <c r="E916" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="F916" t="n">
+        <v>0</v>
+      </c>
+      <c r="G916" t="n">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C917" t="n">
+        <v>0</v>
+      </c>
+      <c r="D917" t="n">
+        <v>0</v>
+      </c>
+      <c r="E917" t="n">
+        <v>8</v>
+      </c>
+      <c r="F917" t="n">
+        <v>0</v>
+      </c>
+      <c r="G917" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C918" t="n">
+        <v>0</v>
+      </c>
+      <c r="D918" t="n">
+        <v>0</v>
+      </c>
+      <c r="E918" t="n">
+        <v>8</v>
+      </c>
+      <c r="F918" t="n">
+        <v>0</v>
+      </c>
+      <c r="G918" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C919" t="n">
+        <v>0</v>
+      </c>
+      <c r="D919" t="n">
+        <v>0</v>
+      </c>
+      <c r="E919" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="F919" t="n">
+        <v>0</v>
+      </c>
+      <c r="G919" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C920" t="n">
+        <v>0</v>
+      </c>
+      <c r="D920" t="n">
+        <v>0</v>
+      </c>
+      <c r="E920" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="F920" t="n">
+        <v>0</v>
+      </c>
+      <c r="G920" t="n">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C921" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="D921" t="n">
+        <v>10</v>
+      </c>
+      <c r="E921" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="F921" t="n">
+        <v>10</v>
+      </c>
+      <c r="G921" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C922" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D922" t="n">
+        <v>38</v>
+      </c>
+      <c r="E922" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F922" t="n">
+        <v>38</v>
+      </c>
+      <c r="G922" t="n">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C923" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="D923" t="n">
+        <v>115</v>
+      </c>
+      <c r="E923" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="F923" t="n">
+        <v>115</v>
+      </c>
+      <c r="G923" t="n">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C924" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="D924" t="n">
+        <v>201</v>
+      </c>
+      <c r="E924" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="F924" t="n">
+        <v>201</v>
+      </c>
+      <c r="G924" t="n">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C925" t="n">
+        <v>25.13</v>
+      </c>
+      <c r="D925" t="n">
+        <v>308</v>
+      </c>
+      <c r="E925" t="n">
+        <v>13</v>
+      </c>
+      <c r="F925" t="n">
+        <v>308</v>
+      </c>
+      <c r="G925" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C926" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="D926" t="n">
+        <v>133</v>
+      </c>
+      <c r="E926" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F926" t="n">
+        <v>133</v>
+      </c>
+      <c r="G926" t="n">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C927" t="n">
+        <v>14.61</v>
+      </c>
+      <c r="D927" t="n">
+        <v>179</v>
+      </c>
+      <c r="E927" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F927" t="n">
+        <v>179</v>
+      </c>
+      <c r="G927" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C928" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="D928" t="n">
+        <v>62</v>
+      </c>
+      <c r="E928" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F928" t="n">
+        <v>62</v>
+      </c>
+      <c r="G928" t="n">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C929" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="D929" t="n">
+        <v>104</v>
+      </c>
+      <c r="E929" t="n">
+        <v>12</v>
+      </c>
+      <c r="F929" t="n">
+        <v>104</v>
+      </c>
+      <c r="G929" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C930" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="D930" t="n">
+        <v>40</v>
+      </c>
+      <c r="E930" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="F930" t="n">
+        <v>40</v>
+      </c>
+      <c r="G930" t="n">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C931" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="D931" t="n">
+        <v>28</v>
+      </c>
+      <c r="E931" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F931" t="n">
+        <v>28</v>
+      </c>
+      <c r="G931" t="n">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C932" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="D932" t="n">
+        <v>16</v>
+      </c>
+      <c r="E932" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F932" t="n">
+        <v>16</v>
+      </c>
+      <c r="G932" t="n">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C933" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D933" t="n">
+        <v>2</v>
+      </c>
+      <c r="E933" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="F933" t="n">
+        <v>2</v>
+      </c>
+      <c r="G933" t="n">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C934" t="n">
+        <v>0</v>
+      </c>
+      <c r="D934" t="n">
+        <v>0</v>
+      </c>
+      <c r="E934" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="F934" t="n">
+        <v>0</v>
+      </c>
+      <c r="G934" t="n">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C935" t="n">
+        <v>0</v>
+      </c>
+      <c r="D935" t="n">
+        <v>0</v>
+      </c>
+      <c r="E935" t="n">
+        <v>14</v>
+      </c>
+      <c r="F935" t="n">
+        <v>0</v>
+      </c>
+      <c r="G935" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C936" t="n">
+        <v>0</v>
+      </c>
+      <c r="D936" t="n">
+        <v>0</v>
+      </c>
+      <c r="E936" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F936" t="n">
+        <v>0</v>
+      </c>
+      <c r="G936" t="n">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C937" t="n">
+        <v>0</v>
+      </c>
+      <c r="D937" t="n">
+        <v>0</v>
+      </c>
+      <c r="E937" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F937" t="n">
+        <v>0</v>
+      </c>
+      <c r="G937" t="n">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C938" t="n">
+        <v>0</v>
+      </c>
+      <c r="D938" t="n">
+        <v>0</v>
+      </c>
+      <c r="E938" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="F938" t="n">
+        <v>0</v>
+      </c>
+      <c r="G938" t="n">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C939" t="n">
+        <v>0</v>
+      </c>
+      <c r="D939" t="n">
+        <v>0</v>
+      </c>
+      <c r="E939" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="F939" t="n">
+        <v>0</v>
+      </c>
+      <c r="G939" t="n">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C940" t="n">
+        <v>0</v>
+      </c>
+      <c r="D940" t="n">
+        <v>0</v>
+      </c>
+      <c r="E940" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F940" t="n">
+        <v>0</v>
+      </c>
+      <c r="G940" t="n">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C941" t="n">
+        <v>0</v>
+      </c>
+      <c r="D941" t="n">
+        <v>0</v>
+      </c>
+      <c r="E941" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="F941" t="n">
+        <v>0</v>
+      </c>
+      <c r="G941" t="n">
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C942" t="n">
+        <v>0</v>
+      </c>
+      <c r="D942" t="n">
+        <v>0</v>
+      </c>
+      <c r="E942" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="F942" t="n">
+        <v>0</v>
+      </c>
+      <c r="G942" t="n">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C943" t="n">
+        <v>0</v>
+      </c>
+      <c r="D943" t="n">
+        <v>0</v>
+      </c>
+      <c r="E943" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="F943" t="n">
+        <v>0</v>
+      </c>
+      <c r="G943" t="n">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C944" t="n">
+        <v>0</v>
+      </c>
+      <c r="D944" t="n">
+        <v>0</v>
+      </c>
+      <c r="E944" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F944" t="n">
+        <v>0</v>
+      </c>
+      <c r="G944" t="n">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C945" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="D945" t="n">
+        <v>25</v>
+      </c>
+      <c r="E945" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="F945" t="n">
+        <v>25</v>
+      </c>
+      <c r="G945" t="n">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C946" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="D946" t="n">
+        <v>113</v>
+      </c>
+      <c r="E946" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="F946" t="n">
+        <v>113</v>
+      </c>
+      <c r="G946" t="n">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C947" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="D947" t="n">
+        <v>231</v>
+      </c>
+      <c r="E947" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="F947" t="n">
+        <v>231</v>
+      </c>
+      <c r="G947" t="n">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C948" t="n">
+        <v>39.13</v>
+      </c>
+      <c r="D948" t="n">
+        <v>490</v>
+      </c>
+      <c r="E948" t="n">
+        <v>15</v>
+      </c>
+      <c r="F948" t="n">
+        <v>490</v>
+      </c>
+      <c r="G948" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C949" t="n">
+        <v>46.03</v>
+      </c>
+      <c r="D949" t="n">
+        <v>583</v>
+      </c>
+      <c r="E949" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="F949" t="n">
+        <v>583</v>
+      </c>
+      <c r="G949" t="n">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C950" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="D950" t="n">
+        <v>756</v>
+      </c>
+      <c r="E950" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="F950" t="n">
+        <v>756</v>
+      </c>
+      <c r="G950" t="n">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C951" t="n">
+        <v>62.21</v>
+      </c>
+      <c r="D951" t="n">
+        <v>817</v>
+      </c>
+      <c r="E951" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="F951" t="n">
+        <v>817</v>
+      </c>
+      <c r="G951" t="n">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C952" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="D952" t="n">
+        <v>789</v>
+      </c>
+      <c r="E952" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="F952" t="n">
+        <v>789</v>
+      </c>
+      <c r="G952" t="n">
+        <v>16.6</v>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C953" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="D953" t="n">
+        <v>735</v>
+      </c>
+      <c r="E953" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="F953" t="n">
+        <v>735</v>
+      </c>
+      <c r="G953" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C954" t="n">
+        <v>45.85</v>
+      </c>
+      <c r="D954" t="n">
+        <v>584</v>
+      </c>
+      <c r="E954" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="F954" t="n">
+        <v>584</v>
+      </c>
+      <c r="G954" t="n">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C955" t="n">
+        <v>32.22</v>
+      </c>
+      <c r="D955" t="n">
+        <v>399</v>
+      </c>
+      <c r="E955" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="F955" t="n">
+        <v>399</v>
+      </c>
+      <c r="G955" t="n">
+        <v>15.1</v>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C956" t="n">
+        <v>16.16</v>
+      </c>
+      <c r="D956" t="n">
+        <v>198</v>
+      </c>
+      <c r="E956" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F956" t="n">
+        <v>198</v>
+      </c>
+      <c r="G956" t="n">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C957" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="D957" t="n">
+        <v>39</v>
+      </c>
+      <c r="E957" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="F957" t="n">
+        <v>39</v>
+      </c>
+      <c r="G957" t="n">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C958" t="n">
+        <v>0</v>
+      </c>
+      <c r="D958" t="n">
+        <v>0</v>
+      </c>
+      <c r="E958" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="F958" t="n">
+        <v>0</v>
+      </c>
+      <c r="G958" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C959" t="n">
+        <v>0</v>
+      </c>
+      <c r="D959" t="n">
+        <v>0</v>
+      </c>
+      <c r="E959" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="F959" t="n">
+        <v>0</v>
+      </c>
+      <c r="G959" t="n">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C960" t="n">
+        <v>0</v>
+      </c>
+      <c r="D960" t="n">
+        <v>0</v>
+      </c>
+      <c r="E960" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="F960" t="n">
+        <v>0</v>
+      </c>
+      <c r="G960" t="n">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C961" t="n">
+        <v>0</v>
+      </c>
+      <c r="D961" t="n">
+        <v>0</v>
+      </c>
+      <c r="E961" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="F961" t="n">
+        <v>0</v>
+      </c>
+      <c r="G961" t="n">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C962" t="n">
+        <v>0</v>
+      </c>
+      <c r="D962" t="n">
+        <v>0</v>
+      </c>
+      <c r="E962" t="n">
+        <v>8</v>
+      </c>
+      <c r="F962" t="n">
+        <v>0</v>
+      </c>
+      <c r="G962" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C963" t="n">
+        <v>0</v>
+      </c>
+      <c r="D963" t="n">
+        <v>0</v>
+      </c>
+      <c r="E963" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="F963" t="n">
+        <v>0</v>
+      </c>
+      <c r="G963" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C964" t="n">
+        <v>0</v>
+      </c>
+      <c r="D964" t="n">
+        <v>0</v>
+      </c>
+      <c r="E964" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="F964" t="n">
+        <v>0</v>
+      </c>
+      <c r="G964" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C965" t="n">
+        <v>0</v>
+      </c>
+      <c r="D965" t="n">
+        <v>0</v>
+      </c>
+      <c r="E965" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="F965" t="n">
+        <v>0</v>
+      </c>
+      <c r="G965" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C966" t="n">
+        <v>0</v>
+      </c>
+      <c r="D966" t="n">
+        <v>0</v>
+      </c>
+      <c r="E966" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="F966" t="n">
+        <v>0</v>
+      </c>
+      <c r="G966" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C967" t="n">
+        <v>0</v>
+      </c>
+      <c r="D967" t="n">
+        <v>0</v>
+      </c>
+      <c r="E967" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="F967" t="n">
+        <v>0</v>
+      </c>
+      <c r="G967" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C968" t="n">
+        <v>0</v>
+      </c>
+      <c r="D968" t="n">
+        <v>0</v>
+      </c>
+      <c r="E968" t="n">
+        <v>6</v>
+      </c>
+      <c r="F968" t="n">
+        <v>0</v>
+      </c>
+      <c r="G968" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C969" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="D969" t="n">
+        <v>43</v>
+      </c>
+      <c r="E969" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="F969" t="n">
+        <v>43</v>
+      </c>
+      <c r="G969" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C970" t="n">
+        <v>16.56</v>
+      </c>
+      <c r="D970" t="n">
+        <v>203</v>
+      </c>
+      <c r="E970" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="F970" t="n">
+        <v>203</v>
+      </c>
+      <c r="G970" t="n">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C971" t="n">
+        <v>33.62</v>
+      </c>
+      <c r="D971" t="n">
+        <v>412</v>
+      </c>
+      <c r="E971" t="n">
+        <v>11</v>
+      </c>
+      <c r="F971" t="n">
+        <v>412</v>
+      </c>
+      <c r="G971" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C972" t="n">
+        <v>47.84</v>
+      </c>
+      <c r="D972" t="n">
+        <v>603</v>
+      </c>
+      <c r="E972" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="F972" t="n">
+        <v>603</v>
+      </c>
+      <c r="G972" t="n">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C973" t="n">
+        <v>58.59</v>
+      </c>
+      <c r="D973" t="n">
+        <v>759</v>
+      </c>
+      <c r="E973" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="F973" t="n">
+        <v>759</v>
+      </c>
+      <c r="G973" t="n">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C974" t="n">
+        <v>64.38</v>
+      </c>
+      <c r="D974" t="n">
+        <v>853</v>
+      </c>
+      <c r="E974" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="F974" t="n">
+        <v>853</v>
+      </c>
+      <c r="G974" t="n">
+        <v>17.1</v>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C975" t="n">
+        <v>64.91</v>
+      </c>
+      <c r="D975" t="n">
+        <v>869</v>
+      </c>
+      <c r="E975" t="n">
+        <v>19</v>
+      </c>
+      <c r="F975" t="n">
+        <v>869</v>
+      </c>
+      <c r="G975" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C976" t="n">
+        <v>62.02</v>
+      </c>
+      <c r="D976" t="n">
+        <v>829</v>
+      </c>
+      <c r="E976" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="F976" t="n">
+        <v>829</v>
+      </c>
+      <c r="G976" t="n">
+        <v>19.9</v>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C977" t="n">
+        <v>51.86</v>
+      </c>
+      <c r="D977" t="n">
+        <v>680</v>
+      </c>
+      <c r="E977" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="F977" t="n">
+        <v>680</v>
+      </c>
+      <c r="G977" t="n">
+        <v>20.1</v>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C978" t="n">
+        <v>40.14</v>
+      </c>
+      <c r="D978" t="n">
+        <v>515</v>
+      </c>
+      <c r="E978" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="F978" t="n">
+        <v>515</v>
+      </c>
+      <c r="G978" t="n">
+        <v>20.1</v>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C979" t="n">
+        <v>25.39</v>
+      </c>
+      <c r="D979" t="n">
+        <v>316</v>
+      </c>
+      <c r="E979" t="n">
+        <v>19</v>
+      </c>
+      <c r="F979" t="n">
+        <v>316</v>
+      </c>
+      <c r="G979" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C980" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="D980" t="n">
+        <v>163</v>
+      </c>
+      <c r="E980" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="F980" t="n">
+        <v>163</v>
+      </c>
+      <c r="G980" t="n">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C981" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="D981" t="n">
+        <v>30</v>
+      </c>
+      <c r="E981" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="F981" t="n">
+        <v>30</v>
+      </c>
+      <c r="G981" t="n">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C982" t="n">
+        <v>0</v>
+      </c>
+      <c r="D982" t="n">
+        <v>0</v>
+      </c>
+      <c r="E982" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="F982" t="n">
+        <v>0</v>
+      </c>
+      <c r="G982" t="n">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C983" t="n">
+        <v>0</v>
+      </c>
+      <c r="D983" t="n">
+        <v>0</v>
+      </c>
+      <c r="E983" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="F983" t="n">
+        <v>0</v>
+      </c>
+      <c r="G983" t="n">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C984" t="n">
+        <v>0</v>
+      </c>
+      <c r="D984" t="n">
+        <v>0</v>
+      </c>
+      <c r="E984" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F984" t="n">
+        <v>0</v>
+      </c>
+      <c r="G984" t="n">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C985" t="n">
+        <v>0</v>
+      </c>
+      <c r="D985" t="n">
+        <v>0</v>
+      </c>
+      <c r="E985" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F985" t="n">
+        <v>0</v>
+      </c>
+      <c r="G985" t="n">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C986" t="n">
+        <v>0</v>
+      </c>
+      <c r="D986" t="n">
+        <v>0</v>
+      </c>
+      <c r="E986" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="F986" t="n">
+        <v>0</v>
+      </c>
+      <c r="G986" t="n">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C987" t="n">
+        <v>0</v>
+      </c>
+      <c r="D987" t="n">
+        <v>0</v>
+      </c>
+      <c r="E987" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F987" t="n">
+        <v>0</v>
+      </c>
+      <c r="G987" t="n">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C988" t="n">
+        <v>0</v>
+      </c>
+      <c r="D988" t="n">
+        <v>0</v>
+      </c>
+      <c r="E988" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="F988" t="n">
+        <v>0</v>
+      </c>
+      <c r="G988" t="n">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C989" t="n">
+        <v>0</v>
+      </c>
+      <c r="D989" t="n">
+        <v>0</v>
+      </c>
+      <c r="E989" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="F989" t="n">
+        <v>0</v>
+      </c>
+      <c r="G989" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C990" t="n">
+        <v>0</v>
+      </c>
+      <c r="D990" t="n">
+        <v>0</v>
+      </c>
+      <c r="E990" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F990" t="n">
+        <v>0</v>
+      </c>
+      <c r="G990" t="n">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C991" t="n">
+        <v>0</v>
+      </c>
+      <c r="D991" t="n">
+        <v>0</v>
+      </c>
+      <c r="E991" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="F991" t="n">
+        <v>0</v>
+      </c>
+      <c r="G991" t="n">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C992" t="n">
+        <v>0</v>
+      </c>
+      <c r="D992" t="n">
+        <v>0</v>
+      </c>
+      <c r="E992" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F992" t="n">
+        <v>0</v>
+      </c>
+      <c r="G992" t="n">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C993" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="D993" t="n">
+        <v>45</v>
+      </c>
+      <c r="E993" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="F993" t="n">
+        <v>45</v>
+      </c>
+      <c r="G993" t="n">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C994" t="n">
+        <v>15.59</v>
+      </c>
+      <c r="D994" t="n">
+        <v>191</v>
+      </c>
+      <c r="E994" t="n">
+        <v>12</v>
+      </c>
+      <c r="F994" t="n">
+        <v>191</v>
+      </c>
+      <c r="G994" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C995" t="n">
+        <v>32.56</v>
+      </c>
+      <c r="D995" t="n">
+        <v>400</v>
+      </c>
+      <c r="E995" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="F995" t="n">
+        <v>400</v>
+      </c>
+      <c r="G995" t="n">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C996" t="n">
+        <v>40.33</v>
+      </c>
+      <c r="D996" t="n">
+        <v>506</v>
+      </c>
+      <c r="E996" t="n">
+        <v>15</v>
+      </c>
+      <c r="F996" t="n">
+        <v>506</v>
+      </c>
+      <c r="G996" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C997" t="n">
+        <v>48.07</v>
+      </c>
+      <c r="D997" t="n">
+        <v>615</v>
+      </c>
+      <c r="E997" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="F997" t="n">
+        <v>615</v>
+      </c>
+      <c r="G997" t="n">
+        <v>16.3</v>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C998" t="n">
+        <v>50.19</v>
+      </c>
+      <c r="D998" t="n">
+        <v>647</v>
+      </c>
+      <c r="E998" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="F998" t="n">
+        <v>647</v>
+      </c>
+      <c r="G998" t="n">
+        <v>17.1</v>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C999" t="n">
+        <v>41.93</v>
+      </c>
+      <c r="D999" t="n">
+        <v>533</v>
+      </c>
+      <c r="E999" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="F999" t="n">
+        <v>533</v>
+      </c>
+      <c r="G999" t="n">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C1000" t="n">
+        <v>39.56</v>
+      </c>
+      <c r="D1000" t="n">
+        <v>500</v>
+      </c>
+      <c r="E1000" t="n">
+        <v>17</v>
+      </c>
+      <c r="F1000" t="n">
+        <v>500</v>
+      </c>
+      <c r="G1000" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C1001" t="n">
+        <v>46.51</v>
+      </c>
+      <c r="D1001" t="n">
+        <v>596</v>
+      </c>
+      <c r="E1001" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="F1001" t="n">
+        <v>596</v>
+      </c>
+      <c r="G1001" t="n">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C1002" t="n">
+        <v>29.77</v>
+      </c>
+      <c r="D1002" t="n">
+        <v>370</v>
+      </c>
+      <c r="E1002" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="F1002" t="n">
+        <v>370</v>
+      </c>
+      <c r="G1002" t="n">
+        <v>16.9</v>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C1003" t="n">
+        <v>17.38</v>
+      </c>
+      <c r="D1003" t="n">
+        <v>213</v>
+      </c>
+      <c r="E1003" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="F1003" t="n">
+        <v>213</v>
+      </c>
+      <c r="G1003" t="n">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C1004" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="D1004" t="n">
+        <v>81</v>
+      </c>
+      <c r="E1004" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="F1004" t="n">
+        <v>81</v>
+      </c>
+      <c r="G1004" t="n">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C1005" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="D1005" t="n">
+        <v>17</v>
+      </c>
+      <c r="E1005" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F1005" t="n">
+        <v>17</v>
+      </c>
+      <c r="G1005" t="n">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C1006" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1006" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1006" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="F1006" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1006" t="n">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C1007" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1007" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1007" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="F1007" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1007" t="n">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C1008" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1008" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1008" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F1008" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1008" t="n">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C1009" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1009" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1009" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1009" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1009" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C1010" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1010" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1010" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F1010" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1010" t="n">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C1011" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1011" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1011" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="F1011" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1011" t="n">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C1012" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1012" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1012" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="F1012" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1012" t="n">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C1013" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1013" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1013" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F1013" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1013" t="n">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1014" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1014" t="n">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1015" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="F1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1015" t="n">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1016" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1016" t="n">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C1017" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D1017" t="n">
+        <v>38</v>
+      </c>
+      <c r="E1017" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F1017" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1017" t="n">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C1018" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="D1018" t="n">
+        <v>104</v>
+      </c>
+      <c r="E1018" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F1018" t="n">
+        <v>104</v>
+      </c>
+      <c r="G1018" t="n">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C1019" t="n">
+        <v>22.36</v>
+      </c>
+      <c r="D1019" t="n">
+        <v>274</v>
+      </c>
+      <c r="E1019" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="F1019" t="n">
+        <v>274</v>
+      </c>
+      <c r="G1019" t="n">
+        <v>16.1</v>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C1020" t="n">
+        <v>42.03</v>
+      </c>
+      <c r="D1020" t="n">
+        <v>537</v>
+      </c>
+      <c r="E1020" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F1020" t="n">
+        <v>537</v>
+      </c>
+      <c r="G1020" t="n">
+        <v>18.4</v>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C1021" t="n">
+        <v>49.65</v>
+      </c>
+      <c r="D1021" t="n">
+        <v>648</v>
+      </c>
+      <c r="E1021" t="n">
+        <v>20</v>
+      </c>
+      <c r="F1021" t="n">
+        <v>648</v>
+      </c>
+      <c r="G1021" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C1022" t="n">
+        <v>62.18</v>
+      </c>
+      <c r="D1022" t="n">
+        <v>838</v>
+      </c>
+      <c r="E1022" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F1022" t="n">
+        <v>838</v>
+      </c>
+      <c r="G1022" t="n">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C1023" t="n">
+        <v>63.99</v>
+      </c>
+      <c r="D1023" t="n">
+        <v>867</v>
+      </c>
+      <c r="E1023" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="F1023" t="n">
+        <v>867</v>
+      </c>
+      <c r="G1023" t="n">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C1024" t="n">
+        <v>61.29</v>
+      </c>
+      <c r="D1024" t="n">
+        <v>825</v>
+      </c>
+      <c r="E1024" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="F1024" t="n">
+        <v>825</v>
+      </c>
+      <c r="G1024" t="n">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C1025" t="n">
+        <v>54.74</v>
+      </c>
+      <c r="D1025" t="n">
+        <v>726</v>
+      </c>
+      <c r="E1025" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="F1025" t="n">
+        <v>726</v>
+      </c>
+      <c r="G1025" t="n">
+        <v>21.3</v>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C1026" t="n">
+        <v>35.55</v>
+      </c>
+      <c r="D1026" t="n">
+        <v>453</v>
+      </c>
+      <c r="E1026" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="F1026" t="n">
+        <v>453</v>
+      </c>
+      <c r="G1026" t="n">
+        <v>20.4</v>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C1027" t="n">
+        <v>15.18</v>
+      </c>
+      <c r="D1027" t="n">
+        <v>186</v>
+      </c>
+      <c r="E1027" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F1027" t="n">
+        <v>186</v>
+      </c>
+      <c r="G1027" t="n">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C1028" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="D1028" t="n">
+        <v>90</v>
+      </c>
+      <c r="E1028" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="F1028" t="n">
+        <v>90</v>
+      </c>
+      <c r="G1028" t="n">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C1029" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="D1029" t="n">
+        <v>14</v>
+      </c>
+      <c r="E1029" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="F1029" t="n">
+        <v>14</v>
+      </c>
+      <c r="G1029" t="n">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C1030" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1030" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1030" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="F1030" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1030" t="n">
+        <v>15.1</v>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C1031" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1031" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1031" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F1031" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1031" t="n">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C1032" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1032" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1032" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="F1032" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1032" t="n">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C1033" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1033" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1033" t="n">
+        <v>13</v>
+      </c>
+      <c r="F1033" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1033" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C1034" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1034" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1034" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F1034" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1034" t="n">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1035" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="F1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1035" t="n">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1036" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1036" t="n">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C1037" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1037" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1037" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F1037" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1037" t="n">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C1038" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1038" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1038" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F1038" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1038" t="n">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C1039" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1039" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1039" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="F1039" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1039" t="n">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C1040" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1040" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1040" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="F1040" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1040" t="n">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C1041" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="D1041" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1041" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F1041" t="n">
+        <v>25</v>
+      </c>
+      <c r="G1041" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C1042" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="D1042" t="n">
+        <v>72</v>
+      </c>
+      <c r="E1042" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="F1042" t="n">
+        <v>72</v>
+      </c>
+      <c r="G1042" t="n">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C1043" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="D1043" t="n">
+        <v>76</v>
+      </c>
+      <c r="E1043" t="n">
+        <v>14</v>
+      </c>
+      <c r="F1043" t="n">
+        <v>76</v>
+      </c>
+      <c r="G1043" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C1044" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="D1044" t="n">
+        <v>185</v>
+      </c>
+      <c r="E1044" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="F1044" t="n">
+        <v>185</v>
+      </c>
+      <c r="G1044" t="n">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C1045" t="n">
+        <v>21.62</v>
+      </c>
+      <c r="D1045" t="n">
+        <v>265</v>
+      </c>
+      <c r="E1045" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="F1045" t="n">
+        <v>265</v>
+      </c>
+      <c r="G1045" t="n">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C1046" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="D1046" t="n">
+        <v>272</v>
+      </c>
+      <c r="E1046" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="F1046" t="n">
+        <v>272</v>
+      </c>
+      <c r="G1046" t="n">
+        <v>16.3</v>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C1047" t="n">
+        <v>20.56</v>
+      </c>
+      <c r="D1047" t="n">
+        <v>252</v>
+      </c>
+      <c r="E1047" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="F1047" t="n">
+        <v>252</v>
+      </c>
+      <c r="G1047" t="n">
+        <v>16.4</v>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C1048" t="n">
+        <v>35.62</v>
+      </c>
+      <c r="D1048" t="n">
+        <v>448</v>
+      </c>
+      <c r="E1048" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="F1048" t="n">
+        <v>448</v>
+      </c>
+      <c r="G1048" t="n">
+        <v>17.4</v>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C1049" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="D1049" t="n">
+        <v>239</v>
+      </c>
+      <c r="E1049" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="F1049" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1049" t="n">
+        <v>16.1</v>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C1050" t="n">
+        <v>24.09</v>
+      </c>
+      <c r="D1050" t="n">
+        <v>297</v>
+      </c>
+      <c r="E1050" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F1050" t="n">
+        <v>297</v>
+      </c>
+      <c r="G1050" t="n">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C1051" t="n">
+        <v>14.85</v>
+      </c>
+      <c r="D1051" t="n">
+        <v>182</v>
+      </c>
+      <c r="E1051" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="F1051" t="n">
+        <v>182</v>
+      </c>
+      <c r="G1051" t="n">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C1052" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="D1052" t="n">
+        <v>57</v>
+      </c>
+      <c r="E1052" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="F1052" t="n">
+        <v>57</v>
+      </c>
+      <c r="G1052" t="n">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C1053" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="D1053" t="n">
+        <v>16</v>
+      </c>
+      <c r="E1053" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="F1053" t="n">
+        <v>16</v>
+      </c>
+      <c r="G1053" t="n">
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C1054" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1054" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1054" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F1054" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1054" t="n">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C1055" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1055" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1055" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F1055" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1055" t="n">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C1056" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1056" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1056" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="F1056" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1056" t="n">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C1057" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1057" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1057" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="F1057" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1057" t="n">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C1058" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1058" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1058" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="F1058" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1058" t="n">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C1059" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1059" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1059" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="F1059" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1059" t="n">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C1060" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1060" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1060" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="F1060" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1060" t="n">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C1061" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1061" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1061" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F1061" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1061" t="n">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C1062" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1062" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1062" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1062" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1062" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C1063" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1063" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1063" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="F1063" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1063" t="n">
+        <v>9.699999999999999</v>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1064" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1064" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C1065" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D1065" t="n">
+        <v>38</v>
+      </c>
+      <c r="E1065" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="F1065" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1065" t="n">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C1066" t="n">
+        <v>13.06</v>
+      </c>
+      <c r="D1066" t="n">
+        <v>160</v>
+      </c>
+      <c r="E1066" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F1066" t="n">
+        <v>160</v>
+      </c>
+      <c r="G1066" t="n">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C1067" t="n">
+        <v>29.05</v>
+      </c>
+      <c r="D1067" t="n">
+        <v>356</v>
+      </c>
+      <c r="E1067" t="n">
+        <v>13</v>
+      </c>
+      <c r="F1067" t="n">
+        <v>356</v>
+      </c>
+      <c r="G1067" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C1068" t="n">
+        <v>44.51</v>
+      </c>
+      <c r="D1068" t="n">
+        <v>565</v>
+      </c>
+      <c r="E1068" t="n">
+        <v>16</v>
+      </c>
+      <c r="F1068" t="n">
+        <v>565</v>
+      </c>
+      <c r="G1068" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C1069" t="n">
+        <v>57.17</v>
+      </c>
+      <c r="D1069" t="n">
+        <v>751</v>
+      </c>
+      <c r="E1069" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="F1069" t="n">
+        <v>751</v>
+      </c>
+      <c r="G1069" t="n">
+        <v>18.3</v>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C1070" t="n">
+        <v>62.98</v>
+      </c>
+      <c r="D1070" t="n">
+        <v>844</v>
+      </c>
+      <c r="E1070" t="n">
+        <v>20</v>
+      </c>
+      <c r="F1070" t="n">
+        <v>844</v>
+      </c>
+      <c r="G1070" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C1071" t="n">
+        <v>64.70999999999999</v>
+      </c>
+      <c r="D1071" t="n">
+        <v>876</v>
+      </c>
+      <c r="E1071" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="F1071" t="n">
+        <v>876</v>
+      </c>
+      <c r="G1071" t="n">
+        <v>21.3</v>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C1072" t="n">
+        <v>62.34</v>
+      </c>
+      <c r="D1072" t="n">
+        <v>843</v>
+      </c>
+      <c r="E1072" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="F1072" t="n">
+        <v>843</v>
+      </c>
+      <c r="G1072" t="n">
+        <v>22.1</v>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C1073" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="D1073" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1073" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="F1073" t="n">
+        <v>749</v>
+      </c>
+      <c r="G1073" t="n">
+        <v>21.3</v>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C1074" t="n">
+        <v>46.11</v>
+      </c>
+      <c r="D1074" t="n">
+        <v>594</v>
+      </c>
+      <c r="E1074" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F1074" t="n">
+        <v>594</v>
+      </c>
+      <c r="G1074" t="n">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C1075" t="n">
+        <v>31.83</v>
+      </c>
+      <c r="D1075" t="n">
+        <v>396</v>
+      </c>
+      <c r="E1075" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="F1075" t="n">
+        <v>396</v>
+      </c>
+      <c r="G1075" t="n">
+        <v>16.4</v>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C1076" t="n">
+        <v>16.56</v>
+      </c>
+      <c r="D1076" t="n">
+        <v>203</v>
+      </c>
+      <c r="E1076" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="F1076" t="n">
+        <v>203</v>
+      </c>
+      <c r="G1076" t="n">
+        <v>15.1</v>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C1077" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="D1077" t="n">
+        <v>44</v>
+      </c>
+      <c r="E1077" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F1077" t="n">
+        <v>44</v>
+      </c>
+      <c r="G1077" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C1078" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1078" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1078" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="F1078" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1078" t="n">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C1079" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1079" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1079" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F1079" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1079" t="n">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C1080" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1080" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1080" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="F1080" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1080" t="n">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C1081" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1081" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1081" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="F1081" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1081" t="n">
+        <v>10.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/train_log.xlsx
+++ b/train_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1081"/>
+  <dimension ref="A1:G1249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29613,6 +29613,4542 @@
         <v>10.1</v>
       </c>
     </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C1082" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1082" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1082" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F1082" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1082" t="n">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C1083" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1083" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1083" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F1083" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1083" t="n">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C1084" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1084" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1084" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F1084" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1084" t="n">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C1085" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1085" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1085" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F1085" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1085" t="n">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C1086" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1086" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1086" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="F1086" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1086" t="n">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C1087" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1087" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1087" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F1087" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1087" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C1088" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1088" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1088" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="F1088" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1088" t="n">
+        <v>8.800000000000001</v>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C1089" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="D1089" t="n">
+        <v>57</v>
+      </c>
+      <c r="E1089" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="F1089" t="n">
+        <v>57</v>
+      </c>
+      <c r="G1089" t="n">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C1090" t="n">
+        <v>19.09</v>
+      </c>
+      <c r="D1090" t="n">
+        <v>234</v>
+      </c>
+      <c r="E1090" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="F1090" t="n">
+        <v>234</v>
+      </c>
+      <c r="G1090" t="n">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C1091" t="n">
+        <v>35.73</v>
+      </c>
+      <c r="D1091" t="n">
+        <v>442</v>
+      </c>
+      <c r="E1091" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F1091" t="n">
+        <v>442</v>
+      </c>
+      <c r="G1091" t="n">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C1092" t="n">
+        <v>49.69</v>
+      </c>
+      <c r="D1092" t="n">
+        <v>635</v>
+      </c>
+      <c r="E1092" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="F1092" t="n">
+        <v>635</v>
+      </c>
+      <c r="G1092" t="n">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C1093" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="D1093" t="n">
+        <v>785</v>
+      </c>
+      <c r="E1093" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="F1093" t="n">
+        <v>785</v>
+      </c>
+      <c r="G1093" t="n">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C1094" t="n">
+        <v>65.75</v>
+      </c>
+      <c r="D1094" t="n">
+        <v>877</v>
+      </c>
+      <c r="E1094" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="F1094" t="n">
+        <v>877</v>
+      </c>
+      <c r="G1094" t="n">
+        <v>17.9</v>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C1095" t="n">
+        <v>67.31999999999999</v>
+      </c>
+      <c r="D1095" t="n">
+        <v>904</v>
+      </c>
+      <c r="E1095" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F1095" t="n">
+        <v>904</v>
+      </c>
+      <c r="G1095" t="n">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C1096" t="n">
+        <v>64.65000000000001</v>
+      </c>
+      <c r="D1096" t="n">
+        <v>865</v>
+      </c>
+      <c r="E1096" t="n">
+        <v>19</v>
+      </c>
+      <c r="F1096" t="n">
+        <v>865</v>
+      </c>
+      <c r="G1096" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C1097" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="D1097" t="n">
+        <v>772</v>
+      </c>
+      <c r="E1097" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="F1097" t="n">
+        <v>772</v>
+      </c>
+      <c r="G1097" t="n">
+        <v>19.9</v>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C1098" t="n">
+        <v>47.62</v>
+      </c>
+      <c r="D1098" t="n">
+        <v>618</v>
+      </c>
+      <c r="E1098" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="F1098" t="n">
+        <v>618</v>
+      </c>
+      <c r="G1098" t="n">
+        <v>19.6</v>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C1099" t="n">
+        <v>33.79</v>
+      </c>
+      <c r="D1099" t="n">
+        <v>425</v>
+      </c>
+      <c r="E1099" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="F1099" t="n">
+        <v>425</v>
+      </c>
+      <c r="G1099" t="n">
+        <v>18.1</v>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C1100" t="n">
+        <v>17.79</v>
+      </c>
+      <c r="D1100" t="n">
+        <v>218</v>
+      </c>
+      <c r="E1100" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="F1100" t="n">
+        <v>218</v>
+      </c>
+      <c r="G1100" t="n">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C1101" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="D1101" t="n">
+        <v>48</v>
+      </c>
+      <c r="E1101" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F1101" t="n">
+        <v>48</v>
+      </c>
+      <c r="G1101" t="n">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C1102" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1102" t="n">
+        <v>12</v>
+      </c>
+      <c r="F1102" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1102" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C1103" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1103" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1103" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1103" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C1104" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1104" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="F1104" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1104" t="n">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C1105" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1105" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="F1105" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1105" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C1106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1106" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F1106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1106" t="n">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C1107" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1107" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="F1107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1107" t="n">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C1108" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1108" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1108" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F1108" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1108" t="n">
+        <v>9.800000000000001</v>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C1109" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1109" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1109" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1109" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1109" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C1110" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1110" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F1110" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1110" t="n">
+        <v>9.800000000000001</v>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C1111" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1111" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1111" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="F1111" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1111" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C1112" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1112" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1112" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="F1112" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1112" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C1113" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="D1113" t="n">
+        <v>15</v>
+      </c>
+      <c r="E1113" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="F1113" t="n">
+        <v>15</v>
+      </c>
+      <c r="G1113" t="n">
+        <v>9.699999999999999</v>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C1114" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="D1114" t="n">
+        <v>89</v>
+      </c>
+      <c r="E1114" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F1114" t="n">
+        <v>89</v>
+      </c>
+      <c r="G1114" t="n">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C1115" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="D1115" t="n">
+        <v>109</v>
+      </c>
+      <c r="E1115" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F1115" t="n">
+        <v>109</v>
+      </c>
+      <c r="G1115" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C1116" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="D1116" t="n">
+        <v>105</v>
+      </c>
+      <c r="E1116" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F1116" t="n">
+        <v>105</v>
+      </c>
+      <c r="G1116" t="n">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C1117" t="n">
+        <v>25.05</v>
+      </c>
+      <c r="D1117" t="n">
+        <v>307</v>
+      </c>
+      <c r="E1117" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="F1117" t="n">
+        <v>307</v>
+      </c>
+      <c r="G1117" t="n">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C1118" t="n">
+        <v>26.11</v>
+      </c>
+      <c r="D1118" t="n">
+        <v>320</v>
+      </c>
+      <c r="E1118" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F1118" t="n">
+        <v>320</v>
+      </c>
+      <c r="G1118" t="n">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C1119" t="n">
+        <v>31.07</v>
+      </c>
+      <c r="D1119" t="n">
+        <v>383</v>
+      </c>
+      <c r="E1119" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F1119" t="n">
+        <v>383</v>
+      </c>
+      <c r="G1119" t="n">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C1120" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="D1120" t="n">
+        <v>401</v>
+      </c>
+      <c r="E1120" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="F1120" t="n">
+        <v>401</v>
+      </c>
+      <c r="G1120" t="n">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C1121" t="n">
+        <v>18.44</v>
+      </c>
+      <c r="D1121" t="n">
+        <v>226</v>
+      </c>
+      <c r="E1121" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="F1121" t="n">
+        <v>226</v>
+      </c>
+      <c r="G1121" t="n">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C1122" t="n">
+        <v>15.34</v>
+      </c>
+      <c r="D1122" t="n">
+        <v>188</v>
+      </c>
+      <c r="E1122" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F1122" t="n">
+        <v>188</v>
+      </c>
+      <c r="G1122" t="n">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C1123" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="D1123" t="n">
+        <v>75</v>
+      </c>
+      <c r="E1123" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="F1123" t="n">
+        <v>75</v>
+      </c>
+      <c r="G1123" t="n">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C1124" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="D1124" t="n">
+        <v>68</v>
+      </c>
+      <c r="E1124" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F1124" t="n">
+        <v>68</v>
+      </c>
+      <c r="G1124" t="n">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C1125" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="D1125" t="n">
+        <v>15</v>
+      </c>
+      <c r="E1125" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="F1125" t="n">
+        <v>15</v>
+      </c>
+      <c r="G1125" t="n">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C1126" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1126" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1126" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F1126" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1126" t="n">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C1127" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1127" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1127" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F1127" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1127" t="n">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C1128" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1128" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1128" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="F1128" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1128" t="n">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C1129" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1129" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1129" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="F1129" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1129" t="n">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C1130" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1130" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1130" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="F1130" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1130" t="n">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C1131" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1131" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1131" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="F1131" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1131" t="n">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C1132" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1132" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1132" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="F1132" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1132" t="n">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C1133" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1133" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1133" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="F1133" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1133" t="n">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C1134" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1134" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1134" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="F1134" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1134" t="n">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C1135" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1135" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1135" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F1135" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1135" t="n">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C1136" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1136" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1136" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="F1136" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1136" t="n">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C1137" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="D1137" t="n">
+        <v>17</v>
+      </c>
+      <c r="E1137" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="F1137" t="n">
+        <v>17</v>
+      </c>
+      <c r="G1137" t="n">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C1138" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="D1138" t="n">
+        <v>73</v>
+      </c>
+      <c r="E1138" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F1138" t="n">
+        <v>73</v>
+      </c>
+      <c r="G1138" t="n">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C1139" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="D1139" t="n">
+        <v>90</v>
+      </c>
+      <c r="E1139" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F1139" t="n">
+        <v>90</v>
+      </c>
+      <c r="G1139" t="n">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C1140" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="D1140" t="n">
+        <v>291</v>
+      </c>
+      <c r="E1140" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="F1140" t="n">
+        <v>291</v>
+      </c>
+      <c r="G1140" t="n">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C1141" t="n">
+        <v>49.56</v>
+      </c>
+      <c r="D1141" t="n">
+        <v>641</v>
+      </c>
+      <c r="E1141" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="F1141" t="n">
+        <v>641</v>
+      </c>
+      <c r="G1141" t="n">
+        <v>18.1</v>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C1142" t="n">
+        <v>59.55</v>
+      </c>
+      <c r="D1142" t="n">
+        <v>789</v>
+      </c>
+      <c r="E1142" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="F1142" t="n">
+        <v>789</v>
+      </c>
+      <c r="G1142" t="n">
+        <v>19.1</v>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C1143" t="n">
+        <v>52.31</v>
+      </c>
+      <c r="D1143" t="n">
+        <v>683</v>
+      </c>
+      <c r="E1143" t="n">
+        <v>19</v>
+      </c>
+      <c r="F1143" t="n">
+        <v>683</v>
+      </c>
+      <c r="G1143" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C1144" t="n">
+        <v>53.91</v>
+      </c>
+      <c r="D1144" t="n">
+        <v>708</v>
+      </c>
+      <c r="E1144" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="F1144" t="n">
+        <v>708</v>
+      </c>
+      <c r="G1144" t="n">
+        <v>19.6</v>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C1145" t="n">
+        <v>36.68</v>
+      </c>
+      <c r="D1145" t="n">
+        <v>466</v>
+      </c>
+      <c r="E1145" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="F1145" t="n">
+        <v>466</v>
+      </c>
+      <c r="G1145" t="n">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C1146" t="n">
+        <v>28.04</v>
+      </c>
+      <c r="D1146" t="n">
+        <v>350</v>
+      </c>
+      <c r="E1146" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F1146" t="n">
+        <v>350</v>
+      </c>
+      <c r="G1146" t="n">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C1147" t="n">
+        <v>20.45</v>
+      </c>
+      <c r="D1147" t="n">
+        <v>251</v>
+      </c>
+      <c r="E1147" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F1147" t="n">
+        <v>251</v>
+      </c>
+      <c r="G1147" t="n">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C1148" t="n">
+        <v>11.34</v>
+      </c>
+      <c r="D1148" t="n">
+        <v>139</v>
+      </c>
+      <c r="E1148" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="F1148" t="n">
+        <v>139</v>
+      </c>
+      <c r="G1148" t="n">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C1149" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="D1149" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1149" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="F1149" t="n">
+        <v>25</v>
+      </c>
+      <c r="G1149" t="n">
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C1150" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1150" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1150" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F1150" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1150" t="n">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C1151" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1151" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1151" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F1151" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1151" t="n">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C1152" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1152" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1152" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F1152" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1152" t="n">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C1153" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1153" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1153" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="F1153" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1153" t="n">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C1154" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1154" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1154" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F1154" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1154" t="n">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C1155" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1155" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1155" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="F1155" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1155" t="n">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C1156" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1156" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1156" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="F1156" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1156" t="n">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C1157" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1157" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1157" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F1157" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1157" t="n">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C1158" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1158" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1158" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="F1158" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1158" t="n">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C1159" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1159" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1159" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F1159" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1159" t="n">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C1160" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1160" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1160" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="F1160" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1160" t="n">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C1161" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="D1161" t="n">
+        <v>32</v>
+      </c>
+      <c r="E1161" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F1161" t="n">
+        <v>32</v>
+      </c>
+      <c r="G1161" t="n">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C1162" t="n">
+        <v>8.98</v>
+      </c>
+      <c r="D1162" t="n">
+        <v>110</v>
+      </c>
+      <c r="E1162" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="F1162" t="n">
+        <v>110</v>
+      </c>
+      <c r="G1162" t="n">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C1163" t="n">
+        <v>12.81</v>
+      </c>
+      <c r="D1163" t="n">
+        <v>157</v>
+      </c>
+      <c r="E1163" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="F1163" t="n">
+        <v>157</v>
+      </c>
+      <c r="G1163" t="n">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C1164" t="n">
+        <v>35.64</v>
+      </c>
+      <c r="D1164" t="n">
+        <v>451</v>
+      </c>
+      <c r="E1164" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="F1164" t="n">
+        <v>451</v>
+      </c>
+      <c r="G1164" t="n">
+        <v>18.8</v>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C1165" t="n">
+        <v>34.21</v>
+      </c>
+      <c r="D1165" t="n">
+        <v>433</v>
+      </c>
+      <c r="E1165" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="F1165" t="n">
+        <v>433</v>
+      </c>
+      <c r="G1165" t="n">
+        <v>19.4</v>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C1166" t="n">
+        <v>40.37</v>
+      </c>
+      <c r="D1166" t="n">
+        <v>516</v>
+      </c>
+      <c r="E1166" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F1166" t="n">
+        <v>516</v>
+      </c>
+      <c r="G1166" t="n">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C1167" t="n">
+        <v>44.13</v>
+      </c>
+      <c r="D1167" t="n">
+        <v>570</v>
+      </c>
+      <c r="E1167" t="n">
+        <v>20</v>
+      </c>
+      <c r="F1167" t="n">
+        <v>570</v>
+      </c>
+      <c r="G1167" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C1168" t="n">
+        <v>52.78</v>
+      </c>
+      <c r="D1168" t="n">
+        <v>696</v>
+      </c>
+      <c r="E1168" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="F1168" t="n">
+        <v>696</v>
+      </c>
+      <c r="G1168" t="n">
+        <v>20.9</v>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C1169" t="n">
+        <v>51.45</v>
+      </c>
+      <c r="D1169" t="n">
+        <v>675</v>
+      </c>
+      <c r="E1169" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="F1169" t="n">
+        <v>675</v>
+      </c>
+      <c r="G1169" t="n">
+        <v>20.4</v>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C1170" t="n">
+        <v>39.55</v>
+      </c>
+      <c r="D1170" t="n">
+        <v>508</v>
+      </c>
+      <c r="E1170" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="F1170" t="n">
+        <v>508</v>
+      </c>
+      <c r="G1170" t="n">
+        <v>20.6</v>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C1171" t="n">
+        <v>17.55</v>
+      </c>
+      <c r="D1171" t="n">
+        <v>216</v>
+      </c>
+      <c r="E1171" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="F1171" t="n">
+        <v>216</v>
+      </c>
+      <c r="G1171" t="n">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C1172" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="D1172" t="n">
+        <v>95</v>
+      </c>
+      <c r="E1172" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="F1172" t="n">
+        <v>95</v>
+      </c>
+      <c r="G1172" t="n">
+        <v>17.9</v>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C1173" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="D1173" t="n">
+        <v>33</v>
+      </c>
+      <c r="E1173" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="F1173" t="n">
+        <v>33</v>
+      </c>
+      <c r="G1173" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C1174" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1174" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1174" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="F1174" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1174" t="n">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C1175" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1175" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1175" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="F1175" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1175" t="n">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C1176" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1176" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1176" t="n">
+        <v>14</v>
+      </c>
+      <c r="F1176" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1176" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C1177" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1177" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1177" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="F1177" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1177" t="n">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C1178" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1178" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1178" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="F1178" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1178" t="n">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C1179" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1179" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1179" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="F1179" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1179" t="n">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C1180" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1180" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1180" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="F1180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1180" t="n">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C1181" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1181" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1181" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F1181" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1181" t="n">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C1182" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1182" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1182" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="F1182" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1182" t="n">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C1183" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1183" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1183" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F1183" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1183" t="n">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C1184" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1184" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1184" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="F1184" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1184" t="n">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C1185" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="D1185" t="n">
+        <v>45</v>
+      </c>
+      <c r="E1185" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F1185" t="n">
+        <v>45</v>
+      </c>
+      <c r="G1185" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C1186" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="D1186" t="n">
+        <v>146</v>
+      </c>
+      <c r="E1186" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F1186" t="n">
+        <v>146</v>
+      </c>
+      <c r="G1186" t="n">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C1187" t="n">
+        <v>26.54</v>
+      </c>
+      <c r="D1187" t="n">
+        <v>326</v>
+      </c>
+      <c r="E1187" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="F1187" t="n">
+        <v>326</v>
+      </c>
+      <c r="G1187" t="n">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C1188" t="n">
+        <v>44.97</v>
+      </c>
+      <c r="D1188" t="n">
+        <v>576</v>
+      </c>
+      <c r="E1188" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F1188" t="n">
+        <v>576</v>
+      </c>
+      <c r="G1188" t="n">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C1189" t="n">
+        <v>48.33</v>
+      </c>
+      <c r="D1189" t="n">
+        <v>626</v>
+      </c>
+      <c r="E1189" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F1189" t="n">
+        <v>626</v>
+      </c>
+      <c r="G1189" t="n">
+        <v>18.9</v>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C1190" t="n">
+        <v>56.91</v>
+      </c>
+      <c r="D1190" t="n">
+        <v>754</v>
+      </c>
+      <c r="E1190" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F1190" t="n">
+        <v>754</v>
+      </c>
+      <c r="G1190" t="n">
+        <v>20.2</v>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C1191" t="n">
+        <v>55.36</v>
+      </c>
+      <c r="D1191" t="n">
+        <v>732</v>
+      </c>
+      <c r="E1191" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="F1191" t="n">
+        <v>732</v>
+      </c>
+      <c r="G1191" t="n">
+        <v>20.4</v>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C1192" t="n">
+        <v>46.35</v>
+      </c>
+      <c r="D1192" t="n">
+        <v>602</v>
+      </c>
+      <c r="E1192" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="F1192" t="n">
+        <v>602</v>
+      </c>
+      <c r="G1192" t="n">
+        <v>20.3</v>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C1193" t="n">
+        <v>45.59</v>
+      </c>
+      <c r="D1193" t="n">
+        <v>591</v>
+      </c>
+      <c r="E1193" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F1193" t="n">
+        <v>591</v>
+      </c>
+      <c r="G1193" t="n">
+        <v>20.2</v>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C1194" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="D1194" t="n">
+        <v>346</v>
+      </c>
+      <c r="E1194" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F1194" t="n">
+        <v>346</v>
+      </c>
+      <c r="G1194" t="n">
+        <v>18.9</v>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C1195" t="n">
+        <v>25.21</v>
+      </c>
+      <c r="D1195" t="n">
+        <v>312</v>
+      </c>
+      <c r="E1195" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="F1195" t="n">
+        <v>312</v>
+      </c>
+      <c r="G1195" t="n">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C1196" t="n">
+        <v>14.61</v>
+      </c>
+      <c r="D1196" t="n">
+        <v>179</v>
+      </c>
+      <c r="E1196" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="F1196" t="n">
+        <v>179</v>
+      </c>
+      <c r="G1196" t="n">
+        <v>16.4</v>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C1197" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="D1197" t="n">
+        <v>43</v>
+      </c>
+      <c r="E1197" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="F1197" t="n">
+        <v>43</v>
+      </c>
+      <c r="G1197" t="n">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C1198" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1198" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1198" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="F1198" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1198" t="n">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C1199" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1199" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1199" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F1199" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1199" t="n">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C1200" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1200" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1200" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F1200" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1200" t="n">
+        <v>9.800000000000001</v>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C1201" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1201" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1201" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="F1201" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1201" t="n">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C1202" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1202" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1202" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="F1202" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1202" t="n">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C1203" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1203" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1203" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="F1203" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1203" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C1204" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1204" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1204" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1204" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1204" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C1205" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1205" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1205" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F1205" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1205" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C1206" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1206" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1206" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="F1206" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1206" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C1207" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1207" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1207" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F1207" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1207" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C1208" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1208" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1208" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="F1208" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1208" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C1209" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="D1209" t="n">
+        <v>66</v>
+      </c>
+      <c r="E1209" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="F1209" t="n">
+        <v>66</v>
+      </c>
+      <c r="G1209" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C1210" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="D1210" t="n">
+        <v>239</v>
+      </c>
+      <c r="E1210" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="F1210" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1210" t="n">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C1211" t="n">
+        <v>37.62</v>
+      </c>
+      <c r="D1211" t="n">
+        <v>462</v>
+      </c>
+      <c r="E1211" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F1211" t="n">
+        <v>462</v>
+      </c>
+      <c r="G1211" t="n">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C1212" t="n">
+        <v>52.29</v>
+      </c>
+      <c r="D1212" t="n">
+        <v>665</v>
+      </c>
+      <c r="E1212" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F1212" t="n">
+        <v>665</v>
+      </c>
+      <c r="G1212" t="n">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C1213" t="n">
+        <v>62.29</v>
+      </c>
+      <c r="D1213" t="n">
+        <v>812</v>
+      </c>
+      <c r="E1213" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="F1213" t="n">
+        <v>812</v>
+      </c>
+      <c r="G1213" t="n">
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C1214" t="n">
+        <v>68.15000000000001</v>
+      </c>
+      <c r="D1214" t="n">
+        <v>905</v>
+      </c>
+      <c r="E1214" t="n">
+        <v>16</v>
+      </c>
+      <c r="F1214" t="n">
+        <v>905</v>
+      </c>
+      <c r="G1214" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C1215" t="n">
+        <v>69.62</v>
+      </c>
+      <c r="D1215" t="n">
+        <v>932</v>
+      </c>
+      <c r="E1215" t="n">
+        <v>17</v>
+      </c>
+      <c r="F1215" t="n">
+        <v>932</v>
+      </c>
+      <c r="G1215" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C1216" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="D1216" t="n">
+        <v>889</v>
+      </c>
+      <c r="E1216" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="F1216" t="n">
+        <v>889</v>
+      </c>
+      <c r="G1216" t="n">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C1217" t="n">
+        <v>59.69</v>
+      </c>
+      <c r="D1217" t="n">
+        <v>785</v>
+      </c>
+      <c r="E1217" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F1217" t="n">
+        <v>785</v>
+      </c>
+      <c r="G1217" t="n">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C1218" t="n">
+        <v>49.24</v>
+      </c>
+      <c r="D1218" t="n">
+        <v>633</v>
+      </c>
+      <c r="E1218" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="F1218" t="n">
+        <v>633</v>
+      </c>
+      <c r="G1218" t="n">
+        <v>16.9</v>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C1219" t="n">
+        <v>35.09</v>
+      </c>
+      <c r="D1219" t="n">
+        <v>437</v>
+      </c>
+      <c r="E1219" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="F1219" t="n">
+        <v>437</v>
+      </c>
+      <c r="G1219" t="n">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C1220" t="n">
+        <v>18.52</v>
+      </c>
+      <c r="D1220" t="n">
+        <v>227</v>
+      </c>
+      <c r="E1220" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="F1220" t="n">
+        <v>227</v>
+      </c>
+      <c r="G1220" t="n">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C1221" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="D1221" t="n">
+        <v>55</v>
+      </c>
+      <c r="E1221" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="F1221" t="n">
+        <v>55</v>
+      </c>
+      <c r="G1221" t="n">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C1222" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1222" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1222" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1222" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1222" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C1223" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1223" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1223" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="F1223" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1223" t="n">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C1224" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1224" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1224" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="F1224" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1224" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C1225" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1225" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1225" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1225" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1225" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C1226" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1226" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1226" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="F1226" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1226" t="n">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C1227" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1227" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1227" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F1227" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1227" t="n">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C1228" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1228" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1228" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="F1228" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1228" t="n">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C1229" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1229" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1229" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="F1229" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1229" t="n">
+        <v>9.699999999999999</v>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C1230" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1230" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1230" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="F1230" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1230" t="n">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C1231" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1231" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1231" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F1231" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1231" t="n">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C1232" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1232" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1232" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1232" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1232" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C1233" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="D1233" t="n">
+        <v>15</v>
+      </c>
+      <c r="E1233" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="F1233" t="n">
+        <v>15</v>
+      </c>
+      <c r="G1233" t="n">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C1234" t="n">
+        <v>4</v>
+      </c>
+      <c r="D1234" t="n">
+        <v>49</v>
+      </c>
+      <c r="E1234" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F1234" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1234" t="n">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C1235" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="D1235" t="n">
+        <v>95</v>
+      </c>
+      <c r="E1235" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="F1235" t="n">
+        <v>95</v>
+      </c>
+      <c r="G1235" t="n">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C1236" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="D1236" t="n">
+        <v>155</v>
+      </c>
+      <c r="E1236" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="F1236" t="n">
+        <v>155</v>
+      </c>
+      <c r="G1236" t="n">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C1237" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="D1237" t="n">
+        <v>126</v>
+      </c>
+      <c r="E1237" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F1237" t="n">
+        <v>126</v>
+      </c>
+      <c r="G1237" t="n">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C1238" t="n">
+        <v>13.06</v>
+      </c>
+      <c r="D1238" t="n">
+        <v>160</v>
+      </c>
+      <c r="E1238" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="F1238" t="n">
+        <v>160</v>
+      </c>
+      <c r="G1238" t="n">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C1239" t="n">
+        <v>14.52</v>
+      </c>
+      <c r="D1239" t="n">
+        <v>178</v>
+      </c>
+      <c r="E1239" t="n">
+        <v>13</v>
+      </c>
+      <c r="F1239" t="n">
+        <v>178</v>
+      </c>
+      <c r="G1239" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C1240" t="n">
+        <v>17.22</v>
+      </c>
+      <c r="D1240" t="n">
+        <v>211</v>
+      </c>
+      <c r="E1240" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F1240" t="n">
+        <v>211</v>
+      </c>
+      <c r="G1240" t="n">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C1241" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="D1241" t="n">
+        <v>136</v>
+      </c>
+      <c r="E1241" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="F1241" t="n">
+        <v>136</v>
+      </c>
+      <c r="G1241" t="n">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C1242" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="D1242" t="n">
+        <v>109</v>
+      </c>
+      <c r="E1242" t="n">
+        <v>12</v>
+      </c>
+      <c r="F1242" t="n">
+        <v>109</v>
+      </c>
+      <c r="G1242" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C1243" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="D1243" t="n">
+        <v>45</v>
+      </c>
+      <c r="E1243" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F1243" t="n">
+        <v>45</v>
+      </c>
+      <c r="G1243" t="n">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C1244" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="D1244" t="n">
+        <v>29</v>
+      </c>
+      <c r="E1244" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="F1244" t="n">
+        <v>29</v>
+      </c>
+      <c r="G1244" t="n">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C1245" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="D1245" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1245" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="F1245" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1245" t="n">
+        <v>9.699999999999999</v>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C1246" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1246" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1246" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1246" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1246" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C1247" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1247" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1247" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="F1247" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1247" t="n">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C1248" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1248" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1248" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="F1248" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1248" t="n">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C1249" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1249" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1249" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="F1249" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1249" t="n">
+        <v>9.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/train_log.xlsx
+++ b/train_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1537"/>
+  <dimension ref="A1:G1561"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41925,6 +41925,654 @@
         <v>24.6</v>
       </c>
     </row>
+    <row r="1538">
+      <c r="A1538" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1538" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C1538" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1538" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1538" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F1538" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1538" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="A1539" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1539" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C1539" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1539" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1539" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="F1539" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1539" t="n">
+        <v>24.1</v>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="A1540" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1540" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C1540" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1540" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1540" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="F1540" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1540" t="n">
+        <v>24.1</v>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1541" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C1541" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1541" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1541" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="F1541" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1541" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="A1542" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1542" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C1542" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1542" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1542" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="F1542" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1542" t="n">
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="A1543" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1543" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C1543" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1543" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1543" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="F1543" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1543" t="n">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1544" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C1544" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D1544" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1544" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="F1544" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1544" t="n">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="A1545" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1545" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C1545" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="D1545" t="n">
+        <v>40</v>
+      </c>
+      <c r="E1545" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="F1545" t="n">
+        <v>40</v>
+      </c>
+      <c r="G1545" t="n">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1546" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C1546" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="D1546" t="n">
+        <v>91</v>
+      </c>
+      <c r="E1546" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="F1546" t="n">
+        <v>91</v>
+      </c>
+      <c r="G1546" t="n">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="A1547" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1547" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C1547" t="n">
+        <v>17.49</v>
+      </c>
+      <c r="D1547" t="n">
+        <v>220</v>
+      </c>
+      <c r="E1547" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F1547" t="n">
+        <v>220</v>
+      </c>
+      <c r="G1547" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="A1548" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1548" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C1548" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="D1548" t="n">
+        <v>258</v>
+      </c>
+      <c r="E1548" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="F1548" t="n">
+        <v>258</v>
+      </c>
+      <c r="G1548" t="n">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="1549">
+      <c r="A1549" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1549" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C1549" t="n">
+        <v>24.62</v>
+      </c>
+      <c r="D1549" t="n">
+        <v>315</v>
+      </c>
+      <c r="E1549" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="F1549" t="n">
+        <v>315</v>
+      </c>
+      <c r="G1549" t="n">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="1550">
+      <c r="A1550" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1550" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C1550" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="D1550" t="n">
+        <v>498</v>
+      </c>
+      <c r="E1550" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="F1550" t="n">
+        <v>498</v>
+      </c>
+      <c r="G1550" t="n">
+        <v>26.9</v>
+      </c>
+    </row>
+    <row r="1551">
+      <c r="A1551" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1551" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C1551" t="n">
+        <v>52.33</v>
+      </c>
+      <c r="D1551" t="n">
+        <v>716</v>
+      </c>
+      <c r="E1551" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="F1551" t="n">
+        <v>716</v>
+      </c>
+      <c r="G1551" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1552" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C1552" t="n">
+        <v>47.77</v>
+      </c>
+      <c r="D1552" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1552" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="F1552" t="n">
+        <v>649</v>
+      </c>
+      <c r="G1552" t="n">
+        <v>29.2</v>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1553" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C1553" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="D1553" t="n">
+        <v>672</v>
+      </c>
+      <c r="E1553" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="F1553" t="n">
+        <v>672</v>
+      </c>
+      <c r="G1553" t="n">
+        <v>28.9</v>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1554" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C1554" t="n">
+        <v>38.05</v>
+      </c>
+      <c r="D1554" t="n">
+        <v>507</v>
+      </c>
+      <c r="E1554" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="F1554" t="n">
+        <v>507</v>
+      </c>
+      <c r="G1554" t="n">
+        <v>29.2</v>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1555" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C1555" t="n">
+        <v>29.67</v>
+      </c>
+      <c r="D1555" t="n">
+        <v>389</v>
+      </c>
+      <c r="E1555" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="F1555" t="n">
+        <v>389</v>
+      </c>
+      <c r="G1555" t="n">
+        <v>29.2</v>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1556" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C1556" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="D1556" t="n">
+        <v>265</v>
+      </c>
+      <c r="E1556" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="F1556" t="n">
+        <v>265</v>
+      </c>
+      <c r="G1556" t="n">
+        <v>28.6</v>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1557" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C1557" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="D1557" t="n">
+        <v>103</v>
+      </c>
+      <c r="E1557" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="F1557" t="n">
+        <v>103</v>
+      </c>
+      <c r="G1557" t="n">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1558" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C1558" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="D1558" t="n">
+        <v>13</v>
+      </c>
+      <c r="E1558" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="F1558" t="n">
+        <v>13</v>
+      </c>
+      <c r="G1558" t="n">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1559" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C1559" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1559" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1559" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="F1559" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1559" t="n">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1560" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C1560" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1560" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1560" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="F1560" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1560" t="n">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1561" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C1561" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1561" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1561" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="F1561" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1561" t="n">
+        <v>24.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/train_log.xlsx
+++ b/train_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1561"/>
+  <dimension ref="A1:G1585"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42573,6 +42573,654 @@
         <v>24.3</v>
       </c>
     </row>
+    <row r="1562">
+      <c r="A1562" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1562" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C1562" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1562" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1562" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="F1562" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1562" t="n">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1563" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C1563" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1563" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1563" t="n">
+        <v>23</v>
+      </c>
+      <c r="F1563" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1563" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="A1564" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1564" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C1564" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1564" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1564" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="F1564" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1564" t="n">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="1565">
+      <c r="A1565" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1565" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C1565" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1565" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1565" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="F1565" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1565" t="n">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="1566">
+      <c r="A1566" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1566" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C1566" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1566" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1566" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="F1566" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1566" t="n">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="1567">
+      <c r="A1567" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1567" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C1567" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1567" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1567" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="F1567" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1567" t="n">
+        <v>22.3</v>
+      </c>
+    </row>
+    <row r="1568">
+      <c r="A1568" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1568" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C1568" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="D1568" t="n">
+        <v>7</v>
+      </c>
+      <c r="E1568" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="F1568" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1568" t="n">
+        <v>22.1</v>
+      </c>
+    </row>
+    <row r="1569">
+      <c r="A1569" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1569" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C1569" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="D1569" t="n">
+        <v>84</v>
+      </c>
+      <c r="E1569" t="n">
+        <v>23</v>
+      </c>
+      <c r="F1569" t="n">
+        <v>84</v>
+      </c>
+      <c r="G1569" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1570">
+      <c r="A1570" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1570" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C1570" t="n">
+        <v>11.68</v>
+      </c>
+      <c r="D1570" t="n">
+        <v>145</v>
+      </c>
+      <c r="E1570" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="F1570" t="n">
+        <v>145</v>
+      </c>
+      <c r="G1570" t="n">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="1571">
+      <c r="A1571" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1571" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C1571" t="n">
+        <v>29.82</v>
+      </c>
+      <c r="D1571" t="n">
+        <v>385</v>
+      </c>
+      <c r="E1571" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="F1571" t="n">
+        <v>385</v>
+      </c>
+      <c r="G1571" t="n">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="1572">
+      <c r="A1572" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1572" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C1572" t="n">
+        <v>44.11</v>
+      </c>
+      <c r="D1572" t="n">
+        <v>588</v>
+      </c>
+      <c r="E1572" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="F1572" t="n">
+        <v>588</v>
+      </c>
+      <c r="G1572" t="n">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="A1573" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1573" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C1573" t="n">
+        <v>57.17</v>
+      </c>
+      <c r="D1573" t="n">
+        <v>790</v>
+      </c>
+      <c r="E1573" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="F1573" t="n">
+        <v>790</v>
+      </c>
+      <c r="G1573" t="n">
+        <v>28.6</v>
+      </c>
+    </row>
+    <row r="1574">
+      <c r="A1574" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1574" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C1574" t="n">
+        <v>60.53</v>
+      </c>
+      <c r="D1574" t="n">
+        <v>847</v>
+      </c>
+      <c r="E1574" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="F1574" t="n">
+        <v>847</v>
+      </c>
+      <c r="G1574" t="n">
+        <v>29.6</v>
+      </c>
+    </row>
+    <row r="1575">
+      <c r="A1575" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1575" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C1575" t="n">
+        <v>61.85</v>
+      </c>
+      <c r="D1575" t="n">
+        <v>869</v>
+      </c>
+      <c r="E1575" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="F1575" t="n">
+        <v>869</v>
+      </c>
+      <c r="G1575" t="n">
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="1576">
+      <c r="A1576" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1576" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C1576" t="n">
+        <v>61.85</v>
+      </c>
+      <c r="D1576" t="n">
+        <v>870</v>
+      </c>
+      <c r="E1576" t="n">
+        <v>30</v>
+      </c>
+      <c r="F1576" t="n">
+        <v>870</v>
+      </c>
+      <c r="G1576" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1577" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C1577" t="n">
+        <v>53.91</v>
+      </c>
+      <c r="D1577" t="n">
+        <v>745</v>
+      </c>
+      <c r="E1577" t="n">
+        <v>30</v>
+      </c>
+      <c r="F1577" t="n">
+        <v>745</v>
+      </c>
+      <c r="G1577" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1578" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C1578" t="n">
+        <v>47.95</v>
+      </c>
+      <c r="D1578" t="n">
+        <v>652</v>
+      </c>
+      <c r="E1578" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="F1578" t="n">
+        <v>652</v>
+      </c>
+      <c r="G1578" t="n">
+        <v>29.3</v>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1579" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C1579" t="n">
+        <v>36.94</v>
+      </c>
+      <c r="D1579" t="n">
+        <v>490</v>
+      </c>
+      <c r="E1579" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="F1579" t="n">
+        <v>490</v>
+      </c>
+      <c r="G1579" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1580" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C1580" t="n">
+        <v>24.09</v>
+      </c>
+      <c r="D1580" t="n">
+        <v>311</v>
+      </c>
+      <c r="E1580" t="n">
+        <v>28</v>
+      </c>
+      <c r="F1580" t="n">
+        <v>311</v>
+      </c>
+      <c r="G1580" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1581" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C1581" t="n">
+        <v>10.73</v>
+      </c>
+      <c r="D1581" t="n">
+        <v>135</v>
+      </c>
+      <c r="E1581" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="F1581" t="n">
+        <v>135</v>
+      </c>
+      <c r="G1581" t="n">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1582" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C1582" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="D1582" t="n">
+        <v>15</v>
+      </c>
+      <c r="E1582" t="n">
+        <v>26</v>
+      </c>
+      <c r="F1582" t="n">
+        <v>15</v>
+      </c>
+      <c r="G1582" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1583" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C1583" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1583" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1583" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="F1583" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1583" t="n">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1584" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C1584" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1584" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1584" t="n">
+        <v>25</v>
+      </c>
+      <c r="F1584" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1584" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1585" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C1585" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1585" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1585" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="F1585" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1585" t="n">
+        <v>24.6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/train_log.xlsx
+++ b/train_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G432"/>
+  <dimension ref="A1:G456"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12090,6 +12090,654 @@
         <v>27</v>
       </c>
     </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C433" t="n">
+        <v>0</v>
+      </c>
+      <c r="D433" t="n">
+        <v>0</v>
+      </c>
+      <c r="E433" t="n">
+        <v>26</v>
+      </c>
+      <c r="F433" t="n">
+        <v>0</v>
+      </c>
+      <c r="G433" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C434" t="n">
+        <v>0</v>
+      </c>
+      <c r="D434" t="n">
+        <v>0</v>
+      </c>
+      <c r="E434" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="F434" t="n">
+        <v>0</v>
+      </c>
+      <c r="G434" t="n">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C435" t="n">
+        <v>0</v>
+      </c>
+      <c r="D435" t="n">
+        <v>0</v>
+      </c>
+      <c r="E435" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F435" t="n">
+        <v>0</v>
+      </c>
+      <c r="G435" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C436" t="n">
+        <v>0</v>
+      </c>
+      <c r="D436" t="n">
+        <v>0</v>
+      </c>
+      <c r="E436" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="F436" t="n">
+        <v>0</v>
+      </c>
+      <c r="G436" t="n">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C437" t="n">
+        <v>0</v>
+      </c>
+      <c r="D437" t="n">
+        <v>0</v>
+      </c>
+      <c r="E437" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="F437" t="n">
+        <v>0</v>
+      </c>
+      <c r="G437" t="n">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C438" t="n">
+        <v>0</v>
+      </c>
+      <c r="D438" t="n">
+        <v>0</v>
+      </c>
+      <c r="E438" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="F438" t="n">
+        <v>0</v>
+      </c>
+      <c r="G438" t="n">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C439" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D439" t="n">
+        <v>4</v>
+      </c>
+      <c r="E439" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="F439" t="n">
+        <v>4</v>
+      </c>
+      <c r="G439" t="n">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C440" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="D440" t="n">
+        <v>105</v>
+      </c>
+      <c r="E440" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="F440" t="n">
+        <v>105</v>
+      </c>
+      <c r="G440" t="n">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C441" t="n">
+        <v>22.96</v>
+      </c>
+      <c r="D441" t="n">
+        <v>294</v>
+      </c>
+      <c r="E441" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F441" t="n">
+        <v>294</v>
+      </c>
+      <c r="G441" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C442" t="n">
+        <v>37.27</v>
+      </c>
+      <c r="D442" t="n">
+        <v>496</v>
+      </c>
+      <c r="E442" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="F442" t="n">
+        <v>496</v>
+      </c>
+      <c r="G442" t="n">
+        <v>29.3</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C443" t="n">
+        <v>49.07</v>
+      </c>
+      <c r="D443" t="n">
+        <v>675</v>
+      </c>
+      <c r="E443" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="F443" t="n">
+        <v>675</v>
+      </c>
+      <c r="G443" t="n">
+        <v>31.2</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C444" t="n">
+        <v>57.49</v>
+      </c>
+      <c r="D444" t="n">
+        <v>815</v>
+      </c>
+      <c r="E444" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="F444" t="n">
+        <v>815</v>
+      </c>
+      <c r="G444" t="n">
+        <v>33.4</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C445" t="n">
+        <v>62.63</v>
+      </c>
+      <c r="D445" t="n">
+        <v>906</v>
+      </c>
+      <c r="E445" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="F445" t="n">
+        <v>906</v>
+      </c>
+      <c r="G445" t="n">
+        <v>34.9</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C446" t="n">
+        <v>64.23</v>
+      </c>
+      <c r="D446" t="n">
+        <v>938</v>
+      </c>
+      <c r="E446" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="F446" t="n">
+        <v>938</v>
+      </c>
+      <c r="G446" t="n">
+        <v>35.9</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C447" t="n">
+        <v>62.27</v>
+      </c>
+      <c r="D447" t="n">
+        <v>910</v>
+      </c>
+      <c r="E447" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="F447" t="n">
+        <v>910</v>
+      </c>
+      <c r="G447" t="n">
+        <v>36.9</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C448" t="n">
+        <v>56.51</v>
+      </c>
+      <c r="D448" t="n">
+        <v>819</v>
+      </c>
+      <c r="E448" t="n">
+        <v>38</v>
+      </c>
+      <c r="F448" t="n">
+        <v>819</v>
+      </c>
+      <c r="G448" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C449" t="n">
+        <v>46.91</v>
+      </c>
+      <c r="D449" t="n">
+        <v>663</v>
+      </c>
+      <c r="E449" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="F449" t="n">
+        <v>663</v>
+      </c>
+      <c r="G449" t="n">
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C450" t="n">
+        <v>36.22</v>
+      </c>
+      <c r="D450" t="n">
+        <v>499</v>
+      </c>
+      <c r="E450" t="n">
+        <v>37</v>
+      </c>
+      <c r="F450" t="n">
+        <v>499</v>
+      </c>
+      <c r="G450" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C451" t="n">
+        <v>22.67</v>
+      </c>
+      <c r="D451" t="n">
+        <v>302</v>
+      </c>
+      <c r="E451" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="F451" t="n">
+        <v>302</v>
+      </c>
+      <c r="G451" t="n">
+        <v>35.6</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C452" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="D452" t="n">
+        <v>125</v>
+      </c>
+      <c r="E452" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="F452" t="n">
+        <v>125</v>
+      </c>
+      <c r="G452" t="n">
+        <v>33.8</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C453" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="D453" t="n">
+        <v>9</v>
+      </c>
+      <c r="E453" t="n">
+        <v>32</v>
+      </c>
+      <c r="F453" t="n">
+        <v>9</v>
+      </c>
+      <c r="G453" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C454" t="n">
+        <v>0</v>
+      </c>
+      <c r="D454" t="n">
+        <v>0</v>
+      </c>
+      <c r="E454" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="F454" t="n">
+        <v>0</v>
+      </c>
+      <c r="G454" t="n">
+        <v>30.8</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C455" t="n">
+        <v>0</v>
+      </c>
+      <c r="D455" t="n">
+        <v>0</v>
+      </c>
+      <c r="E455" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="F455" t="n">
+        <v>0</v>
+      </c>
+      <c r="G455" t="n">
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C456" t="n">
+        <v>0</v>
+      </c>
+      <c r="D456" t="n">
+        <v>0</v>
+      </c>
+      <c r="E456" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="F456" t="n">
+        <v>0</v>
+      </c>
+      <c r="G456" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/train_log.xlsx
+++ b/train_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G456"/>
+  <dimension ref="A1:G624"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12738,6 +12738,4542 @@
         <v>28.7</v>
       </c>
     </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C457" t="n">
+        <v>0</v>
+      </c>
+      <c r="D457" t="n">
+        <v>0</v>
+      </c>
+      <c r="E457" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="F457" t="n">
+        <v>0</v>
+      </c>
+      <c r="G457" t="n">
+        <v>27.9</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C458" t="n">
+        <v>0</v>
+      </c>
+      <c r="D458" t="n">
+        <v>0</v>
+      </c>
+      <c r="E458" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="F458" t="n">
+        <v>0</v>
+      </c>
+      <c r="G458" t="n">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C459" t="n">
+        <v>0</v>
+      </c>
+      <c r="D459" t="n">
+        <v>0</v>
+      </c>
+      <c r="E459" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="F459" t="n">
+        <v>0</v>
+      </c>
+      <c r="G459" t="n">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C460" t="n">
+        <v>0</v>
+      </c>
+      <c r="D460" t="n">
+        <v>0</v>
+      </c>
+      <c r="E460" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="F460" t="n">
+        <v>0</v>
+      </c>
+      <c r="G460" t="n">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C461" t="n">
+        <v>0</v>
+      </c>
+      <c r="D461" t="n">
+        <v>0</v>
+      </c>
+      <c r="E461" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="F461" t="n">
+        <v>0</v>
+      </c>
+      <c r="G461" t="n">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C462" t="n">
+        <v>0</v>
+      </c>
+      <c r="D462" t="n">
+        <v>0</v>
+      </c>
+      <c r="E462" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="F462" t="n">
+        <v>0</v>
+      </c>
+      <c r="G462" t="n">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C463" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D463" t="n">
+        <v>4</v>
+      </c>
+      <c r="E463" t="n">
+        <v>24</v>
+      </c>
+      <c r="F463" t="n">
+        <v>4</v>
+      </c>
+      <c r="G463" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C464" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="D464" t="n">
+        <v>103</v>
+      </c>
+      <c r="E464" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="F464" t="n">
+        <v>103</v>
+      </c>
+      <c r="G464" t="n">
+        <v>26.3</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C465" t="n">
+        <v>22.46</v>
+      </c>
+      <c r="D465" t="n">
+        <v>290</v>
+      </c>
+      <c r="E465" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="F465" t="n">
+        <v>290</v>
+      </c>
+      <c r="G465" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C466" t="n">
+        <v>36.53</v>
+      </c>
+      <c r="D466" t="n">
+        <v>490</v>
+      </c>
+      <c r="E466" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="F466" t="n">
+        <v>490</v>
+      </c>
+      <c r="G466" t="n">
+        <v>31.3</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C467" t="n">
+        <v>48.54</v>
+      </c>
+      <c r="D467" t="n">
+        <v>673</v>
+      </c>
+      <c r="E467" t="n">
+        <v>33</v>
+      </c>
+      <c r="F467" t="n">
+        <v>673</v>
+      </c>
+      <c r="G467" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C468" t="n">
+        <v>57.09</v>
+      </c>
+      <c r="D468" t="n">
+        <v>814</v>
+      </c>
+      <c r="E468" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="F468" t="n">
+        <v>814</v>
+      </c>
+      <c r="G468" t="n">
+        <v>34.7</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C469" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="D469" t="n">
+        <v>907</v>
+      </c>
+      <c r="E469" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="F469" t="n">
+        <v>907</v>
+      </c>
+      <c r="G469" t="n">
+        <v>36.2</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C470" t="n">
+        <v>63.68</v>
+      </c>
+      <c r="D470" t="n">
+        <v>937</v>
+      </c>
+      <c r="E470" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="F470" t="n">
+        <v>937</v>
+      </c>
+      <c r="G470" t="n">
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C471" t="n">
+        <v>61.86</v>
+      </c>
+      <c r="D471" t="n">
+        <v>911</v>
+      </c>
+      <c r="E471" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="F471" t="n">
+        <v>911</v>
+      </c>
+      <c r="G471" t="n">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C472" t="n">
+        <v>56.55</v>
+      </c>
+      <c r="D472" t="n">
+        <v>821</v>
+      </c>
+      <c r="E472" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="F472" t="n">
+        <v>821</v>
+      </c>
+      <c r="G472" t="n">
+        <v>38.3</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C473" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="D473" t="n">
+        <v>687</v>
+      </c>
+      <c r="E473" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="F473" t="n">
+        <v>687</v>
+      </c>
+      <c r="G473" t="n">
+        <v>36.8</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C474" t="n">
+        <v>36.91</v>
+      </c>
+      <c r="D474" t="n">
+        <v>506</v>
+      </c>
+      <c r="E474" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="F474" t="n">
+        <v>506</v>
+      </c>
+      <c r="G474" t="n">
+        <v>35.7</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C475" t="n">
+        <v>23.56</v>
+      </c>
+      <c r="D475" t="n">
+        <v>312</v>
+      </c>
+      <c r="E475" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="F475" t="n">
+        <v>312</v>
+      </c>
+      <c r="G475" t="n">
+        <v>33.9</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C476" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="D476" t="n">
+        <v>121</v>
+      </c>
+      <c r="E476" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="F476" t="n">
+        <v>121</v>
+      </c>
+      <c r="G476" t="n">
+        <v>32.3</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C477" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="D477" t="n">
+        <v>8</v>
+      </c>
+      <c r="E477" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="F477" t="n">
+        <v>8</v>
+      </c>
+      <c r="G477" t="n">
+        <v>31.5</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C478" t="n">
+        <v>0</v>
+      </c>
+      <c r="D478" t="n">
+        <v>0</v>
+      </c>
+      <c r="E478" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="F478" t="n">
+        <v>0</v>
+      </c>
+      <c r="G478" t="n">
+        <v>31.6</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C479" t="n">
+        <v>0</v>
+      </c>
+      <c r="D479" t="n">
+        <v>0</v>
+      </c>
+      <c r="E479" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="F479" t="n">
+        <v>0</v>
+      </c>
+      <c r="G479" t="n">
+        <v>30.7</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C480" t="n">
+        <v>0</v>
+      </c>
+      <c r="D480" t="n">
+        <v>0</v>
+      </c>
+      <c r="E480" t="n">
+        <v>30</v>
+      </c>
+      <c r="F480" t="n">
+        <v>0</v>
+      </c>
+      <c r="G480" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C481" t="n">
+        <v>0</v>
+      </c>
+      <c r="D481" t="n">
+        <v>0</v>
+      </c>
+      <c r="E481" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="F481" t="n">
+        <v>0</v>
+      </c>
+      <c r="G481" t="n">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C482" t="n">
+        <v>0</v>
+      </c>
+      <c r="D482" t="n">
+        <v>0</v>
+      </c>
+      <c r="E482" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="F482" t="n">
+        <v>0</v>
+      </c>
+      <c r="G482" t="n">
+        <v>27.9</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C483" t="n">
+        <v>0</v>
+      </c>
+      <c r="D483" t="n">
+        <v>0</v>
+      </c>
+      <c r="E483" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="F483" t="n">
+        <v>0</v>
+      </c>
+      <c r="G483" t="n">
+        <v>27.4</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C484" t="n">
+        <v>0</v>
+      </c>
+      <c r="D484" t="n">
+        <v>0</v>
+      </c>
+      <c r="E484" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F484" t="n">
+        <v>0</v>
+      </c>
+      <c r="G484" t="n">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C485" t="n">
+        <v>0</v>
+      </c>
+      <c r="D485" t="n">
+        <v>0</v>
+      </c>
+      <c r="E485" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="F485" t="n">
+        <v>0</v>
+      </c>
+      <c r="G485" t="n">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C486" t="n">
+        <v>0</v>
+      </c>
+      <c r="D486" t="n">
+        <v>0</v>
+      </c>
+      <c r="E486" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="F486" t="n">
+        <v>0</v>
+      </c>
+      <c r="G486" t="n">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C487" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="D487" t="n">
+        <v>3</v>
+      </c>
+      <c r="E487" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="F487" t="n">
+        <v>3</v>
+      </c>
+      <c r="G487" t="n">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C488" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="D488" t="n">
+        <v>99</v>
+      </c>
+      <c r="E488" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="F488" t="n">
+        <v>99</v>
+      </c>
+      <c r="G488" t="n">
+        <v>28.2</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C489" t="n">
+        <v>21.78</v>
+      </c>
+      <c r="D489" t="n">
+        <v>283</v>
+      </c>
+      <c r="E489" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="F489" t="n">
+        <v>283</v>
+      </c>
+      <c r="G489" t="n">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C490" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="D490" t="n">
+        <v>481</v>
+      </c>
+      <c r="E490" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="F490" t="n">
+        <v>481</v>
+      </c>
+      <c r="G490" t="n">
+        <v>32.6</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C491" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="D491" t="n">
+        <v>661</v>
+      </c>
+      <c r="E491" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="F491" t="n">
+        <v>661</v>
+      </c>
+      <c r="G491" t="n">
+        <v>33.7</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C492" t="n">
+        <v>56.35</v>
+      </c>
+      <c r="D492" t="n">
+        <v>803</v>
+      </c>
+      <c r="E492" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="F492" t="n">
+        <v>803</v>
+      </c>
+      <c r="G492" t="n">
+        <v>34.9</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C493" t="n">
+        <v>61.53</v>
+      </c>
+      <c r="D493" t="n">
+        <v>892</v>
+      </c>
+      <c r="E493" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="F493" t="n">
+        <v>892</v>
+      </c>
+      <c r="G493" t="n">
+        <v>35.8</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C494" t="n">
+        <v>61.92</v>
+      </c>
+      <c r="D494" t="n">
+        <v>898</v>
+      </c>
+      <c r="E494" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="F494" t="n">
+        <v>898</v>
+      </c>
+      <c r="G494" t="n">
+        <v>35.7</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C495" t="n">
+        <v>60.82</v>
+      </c>
+      <c r="D495" t="n">
+        <v>875</v>
+      </c>
+      <c r="E495" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="F495" t="n">
+        <v>875</v>
+      </c>
+      <c r="G495" t="n">
+        <v>34.7</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C496" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="D496" t="n">
+        <v>788</v>
+      </c>
+      <c r="E496" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="F496" t="n">
+        <v>788</v>
+      </c>
+      <c r="G496" t="n">
+        <v>34.6</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C497" t="n">
+        <v>45.94</v>
+      </c>
+      <c r="D497" t="n">
+        <v>634</v>
+      </c>
+      <c r="E497" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="F497" t="n">
+        <v>634</v>
+      </c>
+      <c r="G497" t="n">
+        <v>33.2</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C498" t="n">
+        <v>32.85</v>
+      </c>
+      <c r="D498" t="n">
+        <v>439</v>
+      </c>
+      <c r="E498" t="n">
+        <v>32</v>
+      </c>
+      <c r="F498" t="n">
+        <v>439</v>
+      </c>
+      <c r="G498" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C499" t="n">
+        <v>22.27</v>
+      </c>
+      <c r="D499" t="n">
+        <v>289</v>
+      </c>
+      <c r="E499" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="F499" t="n">
+        <v>289</v>
+      </c>
+      <c r="G499" t="n">
+        <v>29.9</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C500" t="n">
+        <v>9.029999999999999</v>
+      </c>
+      <c r="D500" t="n">
+        <v>114</v>
+      </c>
+      <c r="E500" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="F500" t="n">
+        <v>114</v>
+      </c>
+      <c r="G500" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C501" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="D501" t="n">
+        <v>7</v>
+      </c>
+      <c r="E501" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="F501" t="n">
+        <v>7</v>
+      </c>
+      <c r="G501" t="n">
+        <v>28.2</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C502" t="n">
+        <v>0</v>
+      </c>
+      <c r="D502" t="n">
+        <v>0</v>
+      </c>
+      <c r="E502" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="F502" t="n">
+        <v>0</v>
+      </c>
+      <c r="G502" t="n">
+        <v>28.6</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C503" t="n">
+        <v>0</v>
+      </c>
+      <c r="D503" t="n">
+        <v>0</v>
+      </c>
+      <c r="E503" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="F503" t="n">
+        <v>0</v>
+      </c>
+      <c r="G503" t="n">
+        <v>27.9</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C504" t="n">
+        <v>0</v>
+      </c>
+      <c r="D504" t="n">
+        <v>0</v>
+      </c>
+      <c r="E504" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="F504" t="n">
+        <v>0</v>
+      </c>
+      <c r="G504" t="n">
+        <v>27.4</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C505" t="n">
+        <v>0</v>
+      </c>
+      <c r="D505" t="n">
+        <v>0</v>
+      </c>
+      <c r="E505" t="n">
+        <v>27</v>
+      </c>
+      <c r="F505" t="n">
+        <v>0</v>
+      </c>
+      <c r="G505" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C506" t="n">
+        <v>0</v>
+      </c>
+      <c r="D506" t="n">
+        <v>0</v>
+      </c>
+      <c r="E506" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="F506" t="n">
+        <v>0</v>
+      </c>
+      <c r="G506" t="n">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C507" t="n">
+        <v>0</v>
+      </c>
+      <c r="D507" t="n">
+        <v>0</v>
+      </c>
+      <c r="E507" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="F507" t="n">
+        <v>0</v>
+      </c>
+      <c r="G507" t="n">
+        <v>26.3</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C508" t="n">
+        <v>0</v>
+      </c>
+      <c r="D508" t="n">
+        <v>0</v>
+      </c>
+      <c r="E508" t="n">
+        <v>26</v>
+      </c>
+      <c r="F508" t="n">
+        <v>0</v>
+      </c>
+      <c r="G508" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C509" t="n">
+        <v>0</v>
+      </c>
+      <c r="D509" t="n">
+        <v>0</v>
+      </c>
+      <c r="E509" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="F509" t="n">
+        <v>0</v>
+      </c>
+      <c r="G509" t="n">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C510" t="n">
+        <v>0</v>
+      </c>
+      <c r="D510" t="n">
+        <v>0</v>
+      </c>
+      <c r="E510" t="n">
+        <v>25</v>
+      </c>
+      <c r="F510" t="n">
+        <v>0</v>
+      </c>
+      <c r="G510" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C511" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="D511" t="n">
+        <v>3</v>
+      </c>
+      <c r="E511" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="F511" t="n">
+        <v>3</v>
+      </c>
+      <c r="G511" t="n">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C512" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="D512" t="n">
+        <v>89</v>
+      </c>
+      <c r="E512" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="F512" t="n">
+        <v>89</v>
+      </c>
+      <c r="G512" t="n">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C513" t="n">
+        <v>20.81</v>
+      </c>
+      <c r="D513" t="n">
+        <v>268</v>
+      </c>
+      <c r="E513" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="F513" t="n">
+        <v>268</v>
+      </c>
+      <c r="G513" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C514" t="n">
+        <v>34.63</v>
+      </c>
+      <c r="D514" t="n">
+        <v>463</v>
+      </c>
+      <c r="E514" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="F514" t="n">
+        <v>463</v>
+      </c>
+      <c r="G514" t="n">
+        <v>31.4</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C515" t="n">
+        <v>44.37</v>
+      </c>
+      <c r="D515" t="n">
+        <v>608</v>
+      </c>
+      <c r="E515" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="F515" t="n">
+        <v>608</v>
+      </c>
+      <c r="G515" t="n">
+        <v>32.4</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C516" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="D516" t="n">
+        <v>724</v>
+      </c>
+      <c r="E516" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="F516" t="n">
+        <v>724</v>
+      </c>
+      <c r="G516" t="n">
+        <v>33.6</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C517" t="n">
+        <v>55.87</v>
+      </c>
+      <c r="D517" t="n">
+        <v>794</v>
+      </c>
+      <c r="E517" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="F517" t="n">
+        <v>794</v>
+      </c>
+      <c r="G517" t="n">
+        <v>34.6</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C518" t="n">
+        <v>58.52</v>
+      </c>
+      <c r="D518" t="n">
+        <v>835</v>
+      </c>
+      <c r="E518" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="F518" t="n">
+        <v>835</v>
+      </c>
+      <c r="G518" t="n">
+        <v>34.2</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C519" t="n">
+        <v>56.41</v>
+      </c>
+      <c r="D519" t="n">
+        <v>787</v>
+      </c>
+      <c r="E519" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="F519" t="n">
+        <v>787</v>
+      </c>
+      <c r="G519" t="n">
+        <v>30.8</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C520" t="n">
+        <v>52.17</v>
+      </c>
+      <c r="D520" t="n">
+        <v>720</v>
+      </c>
+      <c r="E520" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="F520" t="n">
+        <v>720</v>
+      </c>
+      <c r="G520" t="n">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C521" t="n">
+        <v>43.68</v>
+      </c>
+      <c r="D521" t="n">
+        <v>591</v>
+      </c>
+      <c r="E521" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="F521" t="n">
+        <v>591</v>
+      </c>
+      <c r="G521" t="n">
+        <v>30.1</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C522" t="n">
+        <v>34.59</v>
+      </c>
+      <c r="D522" t="n">
+        <v>461</v>
+      </c>
+      <c r="E522" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="F522" t="n">
+        <v>461</v>
+      </c>
+      <c r="G522" t="n">
+        <v>30.7</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C523" t="n">
+        <v>20.19</v>
+      </c>
+      <c r="D523" t="n">
+        <v>261</v>
+      </c>
+      <c r="E523" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="F523" t="n">
+        <v>261</v>
+      </c>
+      <c r="G523" t="n">
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C524" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="D524" t="n">
+        <v>102</v>
+      </c>
+      <c r="E524" t="n">
+        <v>29</v>
+      </c>
+      <c r="F524" t="n">
+        <v>102</v>
+      </c>
+      <c r="G524" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C525" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D525" t="n">
+        <v>5</v>
+      </c>
+      <c r="E525" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="F525" t="n">
+        <v>5</v>
+      </c>
+      <c r="G525" t="n">
+        <v>27.9</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C526" t="n">
+        <v>0</v>
+      </c>
+      <c r="D526" t="n">
+        <v>0</v>
+      </c>
+      <c r="E526" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="F526" t="n">
+        <v>0</v>
+      </c>
+      <c r="G526" t="n">
+        <v>28.4</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C527" t="n">
+        <v>0</v>
+      </c>
+      <c r="D527" t="n">
+        <v>0</v>
+      </c>
+      <c r="E527" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="F527" t="n">
+        <v>0</v>
+      </c>
+      <c r="G527" t="n">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C528" t="n">
+        <v>0</v>
+      </c>
+      <c r="D528" t="n">
+        <v>0</v>
+      </c>
+      <c r="E528" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="F528" t="n">
+        <v>0</v>
+      </c>
+      <c r="G528" t="n">
+        <v>26.6</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C529" t="n">
+        <v>0</v>
+      </c>
+      <c r="D529" t="n">
+        <v>0</v>
+      </c>
+      <c r="E529" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="F529" t="n">
+        <v>0</v>
+      </c>
+      <c r="G529" t="n">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C530" t="n">
+        <v>0</v>
+      </c>
+      <c r="D530" t="n">
+        <v>0</v>
+      </c>
+      <c r="E530" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="F530" t="n">
+        <v>0</v>
+      </c>
+      <c r="G530" t="n">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C531" t="n">
+        <v>0</v>
+      </c>
+      <c r="D531" t="n">
+        <v>0</v>
+      </c>
+      <c r="E531" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F531" t="n">
+        <v>0</v>
+      </c>
+      <c r="G531" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C532" t="n">
+        <v>0</v>
+      </c>
+      <c r="D532" t="n">
+        <v>0</v>
+      </c>
+      <c r="E532" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="F532" t="n">
+        <v>0</v>
+      </c>
+      <c r="G532" t="n">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C533" t="n">
+        <v>0</v>
+      </c>
+      <c r="D533" t="n">
+        <v>0</v>
+      </c>
+      <c r="E533" t="n">
+        <v>25</v>
+      </c>
+      <c r="F533" t="n">
+        <v>0</v>
+      </c>
+      <c r="G533" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C534" t="n">
+        <v>0</v>
+      </c>
+      <c r="D534" t="n">
+        <v>0</v>
+      </c>
+      <c r="E534" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="F534" t="n">
+        <v>0</v>
+      </c>
+      <c r="G534" t="n">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C535" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D535" t="n">
+        <v>2</v>
+      </c>
+      <c r="E535" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="F535" t="n">
+        <v>2</v>
+      </c>
+      <c r="G535" t="n">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C536" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="D536" t="n">
+        <v>87</v>
+      </c>
+      <c r="E536" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="F536" t="n">
+        <v>87</v>
+      </c>
+      <c r="G536" t="n">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C537" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="D537" t="n">
+        <v>255</v>
+      </c>
+      <c r="E537" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="F537" t="n">
+        <v>255</v>
+      </c>
+      <c r="G537" t="n">
+        <v>27.7</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C538" t="n">
+        <v>32.76</v>
+      </c>
+      <c r="D538" t="n">
+        <v>434</v>
+      </c>
+      <c r="E538" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="F538" t="n">
+        <v>434</v>
+      </c>
+      <c r="G538" t="n">
+        <v>30.2</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C539" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="D539" t="n">
+        <v>603</v>
+      </c>
+      <c r="E539" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="F539" t="n">
+        <v>603</v>
+      </c>
+      <c r="G539" t="n">
+        <v>31.2</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C540" t="n">
+        <v>52.08</v>
+      </c>
+      <c r="D540" t="n">
+        <v>724</v>
+      </c>
+      <c r="E540" t="n">
+        <v>32</v>
+      </c>
+      <c r="F540" t="n">
+        <v>724</v>
+      </c>
+      <c r="G540" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C541" t="n">
+        <v>57.87</v>
+      </c>
+      <c r="D541" t="n">
+        <v>818</v>
+      </c>
+      <c r="E541" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="F541" t="n">
+        <v>818</v>
+      </c>
+      <c r="G541" t="n">
+        <v>32.7</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C542" t="n">
+        <v>60.54</v>
+      </c>
+      <c r="D542" t="n">
+        <v>858</v>
+      </c>
+      <c r="E542" t="n">
+        <v>32</v>
+      </c>
+      <c r="F542" t="n">
+        <v>858</v>
+      </c>
+      <c r="G542" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C543" t="n">
+        <v>59.77</v>
+      </c>
+      <c r="D543" t="n">
+        <v>845</v>
+      </c>
+      <c r="E543" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="F543" t="n">
+        <v>845</v>
+      </c>
+      <c r="G543" t="n">
+        <v>31.9</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C544" t="n">
+        <v>53.68</v>
+      </c>
+      <c r="D544" t="n">
+        <v>750</v>
+      </c>
+      <c r="E544" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="F544" t="n">
+        <v>750</v>
+      </c>
+      <c r="G544" t="n">
+        <v>32.3</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C545" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="D545" t="n">
+        <v>604</v>
+      </c>
+      <c r="E545" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="F545" t="n">
+        <v>604</v>
+      </c>
+      <c r="G545" t="n">
+        <v>31.4</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C546" t="n">
+        <v>34.53</v>
+      </c>
+      <c r="D546" t="n">
+        <v>459</v>
+      </c>
+      <c r="E546" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="F546" t="n">
+        <v>459</v>
+      </c>
+      <c r="G546" t="n">
+        <v>30.2</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C547" t="n">
+        <v>21.45</v>
+      </c>
+      <c r="D547" t="n">
+        <v>277</v>
+      </c>
+      <c r="E547" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="F547" t="n">
+        <v>277</v>
+      </c>
+      <c r="G547" t="n">
+        <v>29.1</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C548" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="D548" t="n">
+        <v>107</v>
+      </c>
+      <c r="E548" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="F548" t="n">
+        <v>107</v>
+      </c>
+      <c r="G548" t="n">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C549" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="D549" t="n">
+        <v>6</v>
+      </c>
+      <c r="E549" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="F549" t="n">
+        <v>6</v>
+      </c>
+      <c r="G549" t="n">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C550" t="n">
+        <v>0</v>
+      </c>
+      <c r="D550" t="n">
+        <v>0</v>
+      </c>
+      <c r="E550" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="F550" t="n">
+        <v>0</v>
+      </c>
+      <c r="G550" t="n">
+        <v>26.9</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C551" t="n">
+        <v>0</v>
+      </c>
+      <c r="D551" t="n">
+        <v>0</v>
+      </c>
+      <c r="E551" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="F551" t="n">
+        <v>0</v>
+      </c>
+      <c r="G551" t="n">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C552" t="n">
+        <v>0</v>
+      </c>
+      <c r="D552" t="n">
+        <v>0</v>
+      </c>
+      <c r="E552" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="F552" t="n">
+        <v>0</v>
+      </c>
+      <c r="G552" t="n">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C553" t="n">
+        <v>0</v>
+      </c>
+      <c r="D553" t="n">
+        <v>0</v>
+      </c>
+      <c r="E553" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="F553" t="n">
+        <v>0</v>
+      </c>
+      <c r="G553" t="n">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C554" t="n">
+        <v>0</v>
+      </c>
+      <c r="D554" t="n">
+        <v>0</v>
+      </c>
+      <c r="E554" t="n">
+        <v>25</v>
+      </c>
+      <c r="F554" t="n">
+        <v>0</v>
+      </c>
+      <c r="G554" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C555" t="n">
+        <v>0</v>
+      </c>
+      <c r="D555" t="n">
+        <v>0</v>
+      </c>
+      <c r="E555" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="F555" t="n">
+        <v>0</v>
+      </c>
+      <c r="G555" t="n">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C556" t="n">
+        <v>0</v>
+      </c>
+      <c r="D556" t="n">
+        <v>0</v>
+      </c>
+      <c r="E556" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="F556" t="n">
+        <v>0</v>
+      </c>
+      <c r="G556" t="n">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C557" t="n">
+        <v>0</v>
+      </c>
+      <c r="D557" t="n">
+        <v>0</v>
+      </c>
+      <c r="E557" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="F557" t="n">
+        <v>0</v>
+      </c>
+      <c r="G557" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C558" t="n">
+        <v>0</v>
+      </c>
+      <c r="D558" t="n">
+        <v>0</v>
+      </c>
+      <c r="E558" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="F558" t="n">
+        <v>0</v>
+      </c>
+      <c r="G558" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C559" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D559" t="n">
+        <v>2</v>
+      </c>
+      <c r="E559" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="F559" t="n">
+        <v>2</v>
+      </c>
+      <c r="G559" t="n">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C560" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="D560" t="n">
+        <v>90</v>
+      </c>
+      <c r="E560" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="F560" t="n">
+        <v>90</v>
+      </c>
+      <c r="G560" t="n">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C561" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="D561" t="n">
+        <v>272</v>
+      </c>
+      <c r="E561" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="F561" t="n">
+        <v>272</v>
+      </c>
+      <c r="G561" t="n">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C562" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="D562" t="n">
+        <v>471</v>
+      </c>
+      <c r="E562" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="F562" t="n">
+        <v>471</v>
+      </c>
+      <c r="G562" t="n">
+        <v>29.7</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C563" t="n">
+        <v>47.57</v>
+      </c>
+      <c r="D563" t="n">
+        <v>652</v>
+      </c>
+      <c r="E563" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="F563" t="n">
+        <v>652</v>
+      </c>
+      <c r="G563" t="n">
+        <v>31.1</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C564" t="n">
+        <v>56.29</v>
+      </c>
+      <c r="D564" t="n">
+        <v>794</v>
+      </c>
+      <c r="E564" t="n">
+        <v>33</v>
+      </c>
+      <c r="F564" t="n">
+        <v>794</v>
+      </c>
+      <c r="G564" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C565" t="n">
+        <v>61.09</v>
+      </c>
+      <c r="D565" t="n">
+        <v>879</v>
+      </c>
+      <c r="E565" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="F565" t="n">
+        <v>879</v>
+      </c>
+      <c r="G565" t="n">
+        <v>34.6</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C566" t="n">
+        <v>57.51</v>
+      </c>
+      <c r="D566" t="n">
+        <v>817</v>
+      </c>
+      <c r="E566" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="F566" t="n">
+        <v>817</v>
+      </c>
+      <c r="G566" t="n">
+        <v>33.8</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C567" t="n">
+        <v>55.81</v>
+      </c>
+      <c r="D567" t="n">
+        <v>791</v>
+      </c>
+      <c r="E567" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="F567" t="n">
+        <v>791</v>
+      </c>
+      <c r="G567" t="n">
+        <v>34.1</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C568" t="n">
+        <v>55.47</v>
+      </c>
+      <c r="D568" t="n">
+        <v>781</v>
+      </c>
+      <c r="E568" t="n">
+        <v>33</v>
+      </c>
+      <c r="F568" t="n">
+        <v>781</v>
+      </c>
+      <c r="G568" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C569" t="n">
+        <v>46.81</v>
+      </c>
+      <c r="D569" t="n">
+        <v>645</v>
+      </c>
+      <c r="E569" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="F569" t="n">
+        <v>645</v>
+      </c>
+      <c r="G569" t="n">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C570" t="n">
+        <v>37.16</v>
+      </c>
+      <c r="D570" t="n">
+        <v>501</v>
+      </c>
+      <c r="E570" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="F570" t="n">
+        <v>501</v>
+      </c>
+      <c r="G570" t="n">
+        <v>32.1</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C571" t="n">
+        <v>22.95</v>
+      </c>
+      <c r="D571" t="n">
+        <v>300</v>
+      </c>
+      <c r="E571" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="F571" t="n">
+        <v>300</v>
+      </c>
+      <c r="G571" t="n">
+        <v>31.2</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C572" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="D572" t="n">
+        <v>112</v>
+      </c>
+      <c r="E572" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="F572" t="n">
+        <v>112</v>
+      </c>
+      <c r="G572" t="n">
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C573" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="D573" t="n">
+        <v>6</v>
+      </c>
+      <c r="E573" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="F573" t="n">
+        <v>6</v>
+      </c>
+      <c r="G573" t="n">
+        <v>28.3</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C574" t="n">
+        <v>0</v>
+      </c>
+      <c r="D574" t="n">
+        <v>0</v>
+      </c>
+      <c r="E574" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="F574" t="n">
+        <v>0</v>
+      </c>
+      <c r="G574" t="n">
+        <v>28.3</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C575" t="n">
+        <v>0</v>
+      </c>
+      <c r="D575" t="n">
+        <v>0</v>
+      </c>
+      <c r="E575" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="F575" t="n">
+        <v>0</v>
+      </c>
+      <c r="G575" t="n">
+        <v>27.4</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C576" t="n">
+        <v>0</v>
+      </c>
+      <c r="D576" t="n">
+        <v>0</v>
+      </c>
+      <c r="E576" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="F576" t="n">
+        <v>0</v>
+      </c>
+      <c r="G576" t="n">
+        <v>26.6</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C577" t="n">
+        <v>0</v>
+      </c>
+      <c r="D577" t="n">
+        <v>0</v>
+      </c>
+      <c r="E577" t="n">
+        <v>0</v>
+      </c>
+      <c r="F577" t="n">
+        <v>0</v>
+      </c>
+      <c r="G577" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C578" t="n">
+        <v>0</v>
+      </c>
+      <c r="D578" t="n">
+        <v>0</v>
+      </c>
+      <c r="E578" t="n">
+        <v>0</v>
+      </c>
+      <c r="F578" t="n">
+        <v>0</v>
+      </c>
+      <c r="G578" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C579" t="n">
+        <v>0</v>
+      </c>
+      <c r="D579" t="n">
+        <v>0</v>
+      </c>
+      <c r="E579" t="n">
+        <v>0</v>
+      </c>
+      <c r="F579" t="n">
+        <v>0</v>
+      </c>
+      <c r="G579" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C580" t="n">
+        <v>0</v>
+      </c>
+      <c r="D580" t="n">
+        <v>0</v>
+      </c>
+      <c r="E580" t="n">
+        <v>0</v>
+      </c>
+      <c r="F580" t="n">
+        <v>0</v>
+      </c>
+      <c r="G580" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C581" t="n">
+        <v>0</v>
+      </c>
+      <c r="D581" t="n">
+        <v>0</v>
+      </c>
+      <c r="E581" t="n">
+        <v>0</v>
+      </c>
+      <c r="F581" t="n">
+        <v>0</v>
+      </c>
+      <c r="G581" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C582" t="n">
+        <v>0</v>
+      </c>
+      <c r="D582" t="n">
+        <v>0</v>
+      </c>
+      <c r="E582" t="n">
+        <v>0</v>
+      </c>
+      <c r="F582" t="n">
+        <v>0</v>
+      </c>
+      <c r="G582" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C583" t="n">
+        <v>0</v>
+      </c>
+      <c r="D583" t="n">
+        <v>0</v>
+      </c>
+      <c r="E583" t="n">
+        <v>0</v>
+      </c>
+      <c r="F583" t="n">
+        <v>0</v>
+      </c>
+      <c r="G583" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C584" t="n">
+        <v>0</v>
+      </c>
+      <c r="D584" t="n">
+        <v>0</v>
+      </c>
+      <c r="E584" t="n">
+        <v>0</v>
+      </c>
+      <c r="F584" t="n">
+        <v>0</v>
+      </c>
+      <c r="G584" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C585" t="n">
+        <v>0</v>
+      </c>
+      <c r="D585" t="n">
+        <v>0</v>
+      </c>
+      <c r="E585" t="n">
+        <v>0</v>
+      </c>
+      <c r="F585" t="n">
+        <v>0</v>
+      </c>
+      <c r="G585" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C586" t="n">
+        <v>0</v>
+      </c>
+      <c r="D586" t="n">
+        <v>0</v>
+      </c>
+      <c r="E586" t="n">
+        <v>0</v>
+      </c>
+      <c r="F586" t="n">
+        <v>0</v>
+      </c>
+      <c r="G586" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C587" t="n">
+        <v>0</v>
+      </c>
+      <c r="D587" t="n">
+        <v>0</v>
+      </c>
+      <c r="E587" t="n">
+        <v>0</v>
+      </c>
+      <c r="F587" t="n">
+        <v>0</v>
+      </c>
+      <c r="G587" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C588" t="n">
+        <v>0</v>
+      </c>
+      <c r="D588" t="n">
+        <v>0</v>
+      </c>
+      <c r="E588" t="n">
+        <v>0</v>
+      </c>
+      <c r="F588" t="n">
+        <v>0</v>
+      </c>
+      <c r="G588" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C589" t="n">
+        <v>0</v>
+      </c>
+      <c r="D589" t="n">
+        <v>0</v>
+      </c>
+      <c r="E589" t="n">
+        <v>0</v>
+      </c>
+      <c r="F589" t="n">
+        <v>0</v>
+      </c>
+      <c r="G589" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C590" t="n">
+        <v>0</v>
+      </c>
+      <c r="D590" t="n">
+        <v>0</v>
+      </c>
+      <c r="E590" t="n">
+        <v>0</v>
+      </c>
+      <c r="F590" t="n">
+        <v>0</v>
+      </c>
+      <c r="G590" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C591" t="n">
+        <v>0</v>
+      </c>
+      <c r="D591" t="n">
+        <v>0</v>
+      </c>
+      <c r="E591" t="n">
+        <v>0</v>
+      </c>
+      <c r="F591" t="n">
+        <v>0</v>
+      </c>
+      <c r="G591" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C592" t="n">
+        <v>0</v>
+      </c>
+      <c r="D592" t="n">
+        <v>0</v>
+      </c>
+      <c r="E592" t="n">
+        <v>0</v>
+      </c>
+      <c r="F592" t="n">
+        <v>0</v>
+      </c>
+      <c r="G592" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C593" t="n">
+        <v>0</v>
+      </c>
+      <c r="D593" t="n">
+        <v>0</v>
+      </c>
+      <c r="E593" t="n">
+        <v>0</v>
+      </c>
+      <c r="F593" t="n">
+        <v>0</v>
+      </c>
+      <c r="G593" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C594" t="n">
+        <v>0</v>
+      </c>
+      <c r="D594" t="n">
+        <v>0</v>
+      </c>
+      <c r="E594" t="n">
+        <v>0</v>
+      </c>
+      <c r="F594" t="n">
+        <v>0</v>
+      </c>
+      <c r="G594" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C595" t="n">
+        <v>0</v>
+      </c>
+      <c r="D595" t="n">
+        <v>0</v>
+      </c>
+      <c r="E595" t="n">
+        <v>0</v>
+      </c>
+      <c r="F595" t="n">
+        <v>0</v>
+      </c>
+      <c r="G595" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C596" t="n">
+        <v>0</v>
+      </c>
+      <c r="D596" t="n">
+        <v>0</v>
+      </c>
+      <c r="E596" t="n">
+        <v>0</v>
+      </c>
+      <c r="F596" t="n">
+        <v>0</v>
+      </c>
+      <c r="G596" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C597" t="n">
+        <v>0</v>
+      </c>
+      <c r="D597" t="n">
+        <v>0</v>
+      </c>
+      <c r="E597" t="n">
+        <v>0</v>
+      </c>
+      <c r="F597" t="n">
+        <v>0</v>
+      </c>
+      <c r="G597" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C598" t="n">
+        <v>0</v>
+      </c>
+      <c r="D598" t="n">
+        <v>0</v>
+      </c>
+      <c r="E598" t="n">
+        <v>0</v>
+      </c>
+      <c r="F598" t="n">
+        <v>0</v>
+      </c>
+      <c r="G598" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C599" t="n">
+        <v>0</v>
+      </c>
+      <c r="D599" t="n">
+        <v>0</v>
+      </c>
+      <c r="E599" t="n">
+        <v>0</v>
+      </c>
+      <c r="F599" t="n">
+        <v>0</v>
+      </c>
+      <c r="G599" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C600" t="n">
+        <v>0</v>
+      </c>
+      <c r="D600" t="n">
+        <v>0</v>
+      </c>
+      <c r="E600" t="n">
+        <v>0</v>
+      </c>
+      <c r="F600" t="n">
+        <v>0</v>
+      </c>
+      <c r="G600" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C601" t="n">
+        <v>0</v>
+      </c>
+      <c r="D601" t="n">
+        <v>0</v>
+      </c>
+      <c r="E601" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="F601" t="n">
+        <v>0</v>
+      </c>
+      <c r="G601" t="n">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C602" t="n">
+        <v>0</v>
+      </c>
+      <c r="D602" t="n">
+        <v>0</v>
+      </c>
+      <c r="E602" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="F602" t="n">
+        <v>0</v>
+      </c>
+      <c r="G602" t="n">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C603" t="n">
+        <v>0</v>
+      </c>
+      <c r="D603" t="n">
+        <v>0</v>
+      </c>
+      <c r="E603" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F603" t="n">
+        <v>0</v>
+      </c>
+      <c r="G603" t="n">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C604" t="n">
+        <v>0</v>
+      </c>
+      <c r="D604" t="n">
+        <v>0</v>
+      </c>
+      <c r="E604" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F604" t="n">
+        <v>0</v>
+      </c>
+      <c r="G604" t="n">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C605" t="n">
+        <v>0</v>
+      </c>
+      <c r="D605" t="n">
+        <v>0</v>
+      </c>
+      <c r="E605" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="F605" t="n">
+        <v>0</v>
+      </c>
+      <c r="G605" t="n">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C606" t="n">
+        <v>0</v>
+      </c>
+      <c r="D606" t="n">
+        <v>0</v>
+      </c>
+      <c r="E606" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="F606" t="n">
+        <v>0</v>
+      </c>
+      <c r="G606" t="n">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C607" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D607" t="n">
+        <v>1</v>
+      </c>
+      <c r="E607" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="F607" t="n">
+        <v>1</v>
+      </c>
+      <c r="G607" t="n">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C608" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="D608" t="n">
+        <v>30</v>
+      </c>
+      <c r="E608" t="n">
+        <v>23</v>
+      </c>
+      <c r="F608" t="n">
+        <v>30</v>
+      </c>
+      <c r="G608" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C609" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="D609" t="n">
+        <v>79</v>
+      </c>
+      <c r="E609" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F609" t="n">
+        <v>79</v>
+      </c>
+      <c r="G609" t="n">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C610" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="D610" t="n">
+        <v>189</v>
+      </c>
+      <c r="E610" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="F610" t="n">
+        <v>189</v>
+      </c>
+      <c r="G610" t="n">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C611" t="n">
+        <v>28</v>
+      </c>
+      <c r="D611" t="n">
+        <v>363</v>
+      </c>
+      <c r="E611" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="F611" t="n">
+        <v>363</v>
+      </c>
+      <c r="G611" t="n">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C612" t="n">
+        <v>38.94</v>
+      </c>
+      <c r="D612" t="n">
+        <v>519</v>
+      </c>
+      <c r="E612" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="F612" t="n">
+        <v>519</v>
+      </c>
+      <c r="G612" t="n">
+        <v>28.9</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C613" t="n">
+        <v>44.29</v>
+      </c>
+      <c r="D613" t="n">
+        <v>600</v>
+      </c>
+      <c r="E613" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="F613" t="n">
+        <v>600</v>
+      </c>
+      <c r="G613" t="n">
+        <v>30.1</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C614" t="n">
+        <v>53.28</v>
+      </c>
+      <c r="D614" t="n">
+        <v>740</v>
+      </c>
+      <c r="E614" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="F614" t="n">
+        <v>740</v>
+      </c>
+      <c r="G614" t="n">
+        <v>31.3</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C615" t="n">
+        <v>43.66</v>
+      </c>
+      <c r="D615" t="n">
+        <v>593</v>
+      </c>
+      <c r="E615" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="F615" t="n">
+        <v>593</v>
+      </c>
+      <c r="G615" t="n">
+        <v>30.9</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C616" t="n">
+        <v>32.09</v>
+      </c>
+      <c r="D616" t="n">
+        <v>426</v>
+      </c>
+      <c r="E616" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="F616" t="n">
+        <v>426</v>
+      </c>
+      <c r="G616" t="n">
+        <v>30.9</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C617" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="D617" t="n">
+        <v>407</v>
+      </c>
+      <c r="E617" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="F617" t="n">
+        <v>407</v>
+      </c>
+      <c r="G617" t="n">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C618" t="n">
+        <v>26.96</v>
+      </c>
+      <c r="D618" t="n">
+        <v>353</v>
+      </c>
+      <c r="E618" t="n">
+        <v>30</v>
+      </c>
+      <c r="F618" t="n">
+        <v>353</v>
+      </c>
+      <c r="G618" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C619" t="n">
+        <v>15.81</v>
+      </c>
+      <c r="D619" t="n">
+        <v>202</v>
+      </c>
+      <c r="E619" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="F619" t="n">
+        <v>202</v>
+      </c>
+      <c r="G619" t="n">
+        <v>28.9</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C620" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="D620" t="n">
+        <v>71</v>
+      </c>
+      <c r="E620" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="F620" t="n">
+        <v>71</v>
+      </c>
+      <c r="G620" t="n">
+        <v>27.4</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C621" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="D621" t="n">
+        <v>3</v>
+      </c>
+      <c r="E621" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="F621" t="n">
+        <v>3</v>
+      </c>
+      <c r="G621" t="n">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C622" t="n">
+        <v>0</v>
+      </c>
+      <c r="D622" t="n">
+        <v>0</v>
+      </c>
+      <c r="E622" t="n">
+        <v>25</v>
+      </c>
+      <c r="F622" t="n">
+        <v>0</v>
+      </c>
+      <c r="G622" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C623" t="n">
+        <v>0</v>
+      </c>
+      <c r="D623" t="n">
+        <v>0</v>
+      </c>
+      <c r="E623" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="F623" t="n">
+        <v>0</v>
+      </c>
+      <c r="G623" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C624" t="n">
+        <v>0</v>
+      </c>
+      <c r="D624" t="n">
+        <v>0</v>
+      </c>
+      <c r="E624" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F624" t="n">
+        <v>0</v>
+      </c>
+      <c r="G624" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
